--- a/src/attributions/attributions_ig_traj_489.xlsx
+++ b/src/attributions/attributions_ig_traj_489.xlsx
@@ -999,10 +999,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.09087118030703878</v>
+        <v>-0.0851908572144459</v>
       </c>
       <c r="C2" t="n">
         <v>-0</v>
@@ -1011,25 +1011,25 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.008939475049928289</v>
+        <v>-0.02911357313401783</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9852560930192843</v>
+        <v>0.1728780590745953</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>-0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1498863441929005</v>
+        <v>-0.1613301817589261</v>
       </c>
       <c r="L2" t="n">
         <v>-0</v>
@@ -1038,10 +1038,10 @@
         <v>-0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1313634452136433</v>
+        <v>0.05625376758611754</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8874156433052</v>
+        <v>0.1405303225814445</v>
       </c>
       <c r="P2" t="n">
         <v>-0</v>
@@ -1050,40 +1050,40 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>-0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2356315963486168</v>
+        <v>-0.007730343897279481</v>
       </c>
       <c r="U2" t="n">
         <v>-0</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1818798085397729</v>
+        <v>0.02899470812122339</v>
       </c>
       <c r="X2" t="n">
-        <v>0.5027244195681393</v>
+        <v>0.1094620146572941</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.006613400758566287</v>
+        <v>-0.1048514719699685</v>
       </c>
       <c r="AD2" t="n">
         <v>-0</v>
@@ -1092,10 +1092,10 @@
         <v>-0</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.1620002966122161</v>
+        <v>0.02344355490672487</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0.09452299951781384</v>
+        <v>0.01142090067215996</v>
       </c>
       <c r="AH2" t="n">
         <v>-0</v>
@@ -1107,52 +1107,52 @@
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.03372878134227902</v>
+        <v>-0.09045073038496367</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.3435869728913672</v>
+        <v>-0.07218747782240827</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.3642940602674079</v>
+        <v>0.09930449298128907</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
         <v>-0</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.3766390374503877</v>
+        <v>-0.4682753897779915</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW2" t="n">
         <v>-0</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.3629842716679796</v>
+        <v>0.05797260176929021</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.877466857201197</v>
+        <v>0.2502374102093204</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
@@ -1161,10 +1161,10 @@
         <v>-0</v>
       </c>
       <c r="BC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.1842552901505324</v>
+        <v>0.1261763486497303</v>
       </c>
       <c r="BE2" t="n">
         <v>-0</v>
@@ -1173,10 +1173,10 @@
         <v>-0</v>
       </c>
       <c r="BG2" t="n">
-        <v>-0.004896557350504764</v>
+        <v>0.0377572235785076</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.3926844598990905</v>
+        <v>0.1311970049673463</v>
       </c>
       <c r="BI2" t="n">
         <v>-0</v>
@@ -1191,22 +1191,22 @@
         <v>-0</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.335006286761954e-10</v>
+        <v>-9.095747482540147e-11</v>
       </c>
       <c r="BN2" t="n">
         <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.2034777806598542</v>
+        <v>-0.01150886760296216</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.07282609768511526</v>
+        <v>-0.03474263403078343</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS2" t="n">
         <v>0</v>
@@ -1218,22 +1218,22 @@
         <v>-0</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.07912687933160412</v>
+        <v>-0.1444470081022868</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX2" t="n">
         <v>-0</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.3158325041352258</v>
+        <v>0.04803854524336001</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.003826425087584</v>
+        <v>0.2459763379172781</v>
       </c>
       <c r="CA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="n">
         <v>0</v>
@@ -1242,22 +1242,22 @@
         <v>-0</v>
       </c>
       <c r="CD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.1209870265167326</v>
+        <v>0.1821079193306883</v>
       </c>
       <c r="CF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH2" t="n">
-        <v>-0.02806482229199044</v>
+        <v>0.04301064574066169</v>
       </c>
       <c r="CI2" t="n">
-        <v>-0.4506217286139431</v>
+        <v>-0.1267726458940844</v>
       </c>
       <c r="CJ2" t="n">
         <v>-0</v>
@@ -1272,19 +1272,19 @@
         <v>0</v>
       </c>
       <c r="CN2" t="n">
-        <v>-0.008574868066976602</v>
+        <v>0.03936822541923104</v>
       </c>
       <c r="CO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP2" t="n">
         <v>0</v>
       </c>
       <c r="CQ2" t="n">
-        <v>-0.325392730209583</v>
+        <v>-0.05925692004081166</v>
       </c>
       <c r="CR2" t="n">
-        <v>-0.05901939194753381</v>
+        <v>-0.1012502595528021</v>
       </c>
       <c r="CS2" t="n">
         <v>-0</v>
@@ -1299,25 +1299,25 @@
         <v>0</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.07967144161482631</v>
+        <v>0.1850481836179686</v>
       </c>
       <c r="CX2" t="n">
         <v>-0</v>
       </c>
       <c r="CY2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-0.05797710935088854</v>
+        <v>0.01584585872859846</v>
       </c>
       <c r="DA2" t="n">
-        <v>-0.4945769019153459</v>
+        <v>-0.1260866414568201</v>
       </c>
       <c r="DB2" t="n">
         <v>0</v>
       </c>
       <c r="DC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD2" t="n">
         <v>-0</v>
@@ -1326,61 +1326,61 @@
         <v>-0</v>
       </c>
       <c r="DF2" t="n">
-        <v>-0.3563971064927856</v>
+        <v>-0.02960566040574909</v>
       </c>
       <c r="DG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI2" t="n">
-        <v>-0.07474468295043005</v>
+        <v>0.07067956836709274</v>
       </c>
       <c r="DJ2" t="n">
-        <v>-0.04596720069111963</v>
+        <v>-0.1047599890920998</v>
       </c>
       <c r="DK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL2" t="n">
         <v>-0</v>
       </c>
       <c r="DM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN2" t="n">
         <v>-0</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0.2121460344583475</v>
+        <v>0.05118733293656869</v>
       </c>
       <c r="DP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ2" t="n">
         <v>0</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.2181465739953349</v>
+        <v>0.07400244672501813</v>
       </c>
       <c r="DS2" t="n">
-        <v>-0.1234150130672843</v>
+        <v>-0.03980330373135738</v>
       </c>
       <c r="DT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW2" t="n">
         <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.1649647730998183</v>
+        <v>0.1739496088334354</v>
       </c>
       <c r="DY2" t="n">
         <v>0</v>
@@ -1389,10 +1389,10 @@
         <v>-0</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.5386098476203591</v>
+        <v>-0.05721530499092214</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.2940726628722402</v>
+        <v>0.05831924419184453</v>
       </c>
       <c r="EC2" t="n">
         <v>0</v>
@@ -1407,19 +1407,19 @@
         <v>-0</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.1279367035551758</v>
+        <v>0.07123801757606624</v>
       </c>
       <c r="EH2" t="n">
         <v>-0</v>
       </c>
       <c r="EI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ2" t="n">
-        <v>-0.05029262847419026</v>
+        <v>0.07503442720877966</v>
       </c>
       <c r="EK2" t="n">
-        <v>-0.4915999623256777</v>
+        <v>-0.0433665697924871</v>
       </c>
       <c r="EL2" t="n">
         <v>0</v>
@@ -1428,13 +1428,13 @@
         <v>0</v>
       </c>
       <c r="EN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP2" t="n">
-        <v>-0.1589821334675262</v>
+        <v>-0.0375461196560475</v>
       </c>
       <c r="EQ2" t="n">
         <v>0</v>
@@ -1443,37 +1443,37 @@
         <v>-0</v>
       </c>
       <c r="ES2" t="n">
-        <v>-0.2661679743369286</v>
+        <v>0.04876449036322885</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.4628558416194213</v>
+        <v>-0.1147830788007467</v>
       </c>
       <c r="EU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.07124510768433873</v>
+        <v>0.1932191481715204</v>
       </c>
       <c r="EZ2" t="n">
         <v>0</v>
       </c>
       <c r="FA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB2" t="n">
-        <v>-0.1400487677040878</v>
+        <v>0.06416903182259889</v>
       </c>
       <c r="FC2" t="n">
-        <v>-0.4384892693078951</v>
+        <v>-0.1366208387834494</v>
       </c>
       <c r="FD2" t="n">
         <v>-0</v>
@@ -1488,7 +1488,7 @@
         <v>0</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.0005693788727957822</v>
+        <v>0.164247875812741</v>
       </c>
       <c r="FI2" t="n">
         <v>-0</v>
@@ -1497,37 +1497,37 @@
         <v>0</v>
       </c>
       <c r="FK2" t="n">
-        <v>-0.4360161472218517</v>
+        <v>-0.03320190768763454</v>
       </c>
       <c r="FL2" t="n">
-        <v>-0.7172639066016888</v>
+        <v>-0.1286710833346251</v>
       </c>
       <c r="FM2" t="n">
         <v>-0</v>
       </c>
       <c r="FN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO2" t="n">
         <v>-0</v>
       </c>
       <c r="FP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.2053669891660168</v>
+        <v>0.1721997112266858</v>
       </c>
       <c r="FR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS2" t="n">
         <v>0</v>
       </c>
       <c r="FT2" t="n">
-        <v>-0.6297458795231399</v>
+        <v>-0.1052380139513999</v>
       </c>
       <c r="FU2" t="n">
-        <v>-0.3892298748815576</v>
+        <v>-0.06028520181384493</v>
       </c>
       <c r="FV2" t="n">
         <v>0</v>
@@ -1536,31 +1536,31 @@
         <v>0</v>
       </c>
       <c r="FX2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.0218476977339143</v>
+        <v>0.04971811193757619</v>
       </c>
       <c r="GA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.066606203298078</v>
+        <v>-0.03910671339031352</v>
       </c>
       <c r="GE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG2" t="n">
         <v>0</v>
@@ -1568,19 +1568,19 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-0.03798539193868965</v>
+        <v>-0.01200097016337771</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1528214882969173</v>
+        <v>0.04924630276273675</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006101038368321533</v>
+        <v>-0.008440676844602982</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1589,16 +1589,16 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.031696240727344</v>
+        <v>-0.009119904868123854</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1317877447491312</v>
+        <v>0.0629881910659558</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1607,7 +1607,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.02763171961848662</v>
+        <v>-0.01784185693951619</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -1622,22 +1622,22 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.02556490372669408</v>
+        <v>0.008994963066053636</v>
       </c>
       <c r="T3" t="n">
-        <v>0.219109446671976</v>
+        <v>0.01193174887525334</v>
       </c>
       <c r="U3" t="n">
         <v>-0</v>
       </c>
       <c r="V3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1617646746828367</v>
+        <v>-0.004646001542839276</v>
       </c>
       <c r="X3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
         <v>-0</v>
@@ -1649,37 +1649,37 @@
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.08552973010012584</v>
+        <v>-0.003934663772089235</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.1700966552810424</v>
+        <v>2.283544555118825e-05</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.0005111975024292535</v>
+        <v>-0.001154982914554223</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ3" t="n">
         <v>-0</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.02712870794871717</v>
+        <v>-0.005569672864914864</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.08942268923490172</v>
+        <v>0.03346933864818143</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
@@ -1688,25 +1688,25 @@
         <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.1179696017016675</v>
+        <v>0.01879774853371903</v>
       </c>
       <c r="AP3" t="n">
         <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS3" t="n">
         <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.07392279328626702</v>
+        <v>-0.01210504167623355</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.2917539079402436</v>
+        <v>0.08686030788364474</v>
       </c>
       <c r="AV3" t="n">
         <v>-0</v>
@@ -1715,25 +1715,25 @@
         <v>-0</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.4070841057960857</v>
+        <v>-0.02628759365871305</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.04587442147985204</v>
+        <v>-0.0139157256536711</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.05993544695372198</v>
+        <v>0.01081658602845386</v>
       </c>
       <c r="BE3" t="n">
         <v>0</v>
@@ -1742,40 +1742,40 @@
         <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.2267366504306727</v>
+        <v>-0.01432201647077299</v>
       </c>
       <c r="BH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK3" t="n">
         <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0.02988426337216588</v>
+        <v>-0.007622334120438042</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.0832537311336513</v>
+        <v>-0.00800277380885556</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
         <v>-0</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.02945705051398905</v>
+        <v>0.02955134613567785</v>
       </c>
       <c r="BQ3" t="n">
         <v>-0</v>
       </c>
       <c r="BR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
         <v>-0</v>
@@ -1784,103 +1784,103 @@
         <v>-0</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.04851285772828833</v>
+        <v>0.003430573945351161</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.1937323772077254</v>
+        <v>0.0577869131348423</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.1649800376373406</v>
+        <v>-0.005750161737468272</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.008813671447265239</v>
+        <v>0.01101024010680543</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.08406276425849883</v>
+        <v>-0.03711247627414363</v>
       </c>
       <c r="CF3" t="n">
         <v>-0</v>
       </c>
       <c r="CG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0.01615355911149651</v>
+        <v>0.002825278536334856</v>
       </c>
       <c r="CI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL3" t="n">
         <v>-0</v>
       </c>
       <c r="CM3" t="n">
-        <v>-0.02490332409739284</v>
+        <v>0.0004872625826506268</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.01701113438314287</v>
+        <v>-0.0232910327312337</v>
       </c>
       <c r="CO3" t="n">
         <v>-0</v>
       </c>
       <c r="CP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.06474821983372651</v>
+        <v>0.00656113630752251</v>
       </c>
       <c r="CR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV3" t="n">
-        <v>-0.00404276407727525</v>
+        <v>0.005765665929173489</v>
       </c>
       <c r="CW3" t="n">
-        <v>-0.08687088264691127</v>
+        <v>-0.03704216627201935</v>
       </c>
       <c r="CX3" t="n">
         <v>0</v>
       </c>
       <c r="CY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>-0.0260554828480411</v>
+        <v>0.001985197545065182</v>
       </c>
       <c r="DA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB3" t="n">
         <v>0</v>
@@ -1892,37 +1892,37 @@
         <v>0</v>
       </c>
       <c r="DE3" t="n">
-        <v>-0.01034579882909677</v>
+        <v>-0.003339723235392406</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0.1948898037330294</v>
+        <v>-0.03638691687909336</v>
       </c>
       <c r="DG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH3" t="n">
         <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.07101477285676662</v>
+        <v>-0.005866819833428054</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM3" t="n">
         <v>-0</v>
       </c>
       <c r="DN3" t="n">
-        <v>-0.001952214281003763</v>
+        <v>0.003475167834596078</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.06346856106620626</v>
+        <v>-0.02335350427144417</v>
       </c>
       <c r="DP3" t="n">
         <v>-0</v>
@@ -1931,7 +1931,7 @@
         <v>-0</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.04480770680341535</v>
+        <v>-0.0006276103683900111</v>
       </c>
       <c r="DS3" t="n">
         <v>-0</v>
@@ -1940,43 +1940,43 @@
         <v>0</v>
       </c>
       <c r="DU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV3" t="n">
         <v>0</v>
       </c>
       <c r="DW3" t="n">
-        <v>-0.004410818072089457</v>
+        <v>0.01880983163106818</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.08389680211455237</v>
+        <v>0.02309951255456345</v>
       </c>
       <c r="DY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ3" t="n">
         <v>0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.02796392112407499</v>
+        <v>0.0004820964107368712</v>
       </c>
       <c r="EB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC3" t="n">
         <v>-0</v>
       </c>
       <c r="ED3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0.01483521012275884</v>
+        <v>0.003840071328839191</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.02559637599114267</v>
+        <v>-0.02505007260444294</v>
       </c>
       <c r="EH3" t="n">
         <v>-0</v>
@@ -1985,10 +1985,10 @@
         <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.05358049393868938</v>
+        <v>-0.01168123646642071</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL3" t="n">
         <v>-0</v>
@@ -2000,52 +2000,52 @@
         <v>-0</v>
       </c>
       <c r="EO3" t="n">
-        <v>-0.02322160858164177</v>
+        <v>0.004221116004766181</v>
       </c>
       <c r="EP3" t="n">
-        <v>-0.1080524804227009</v>
+        <v>-0.0163924135491004</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0.03861182688781956</v>
+        <v>-0.001351807874871709</v>
       </c>
       <c r="ET3" t="n">
         <v>-0</v>
       </c>
       <c r="EU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV3" t="n">
         <v>-0</v>
       </c>
       <c r="EW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX3" t="n">
-        <v>-0.006960278080620193</v>
+        <v>0.009730672856055007</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0.09625708761523175</v>
+        <v>-0.04146449235652728</v>
       </c>
       <c r="EZ3" t="n">
         <v>-0</v>
       </c>
       <c r="FA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB3" t="n">
-        <v>-0.0654414470345102</v>
+        <v>-0.001447825851795438</v>
       </c>
       <c r="FC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE3" t="n">
         <v>-0</v>
@@ -2054,10 +2054,10 @@
         <v>-0</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.03939578816314845</v>
+        <v>-0.003597276682890966</v>
       </c>
       <c r="FH3" t="n">
-        <v>-0.04822202100521158</v>
+        <v>-0.01917702782474037</v>
       </c>
       <c r="FI3" t="n">
         <v>-0</v>
@@ -2066,10 +2066,10 @@
         <v>-0</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0.0779197050664998</v>
+        <v>0.0106771972870392</v>
       </c>
       <c r="FL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM3" t="n">
         <v>0</v>
@@ -2078,13 +2078,13 @@
         <v>0</v>
       </c>
       <c r="FO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP3" t="n">
-        <v>-0.01016741846000878</v>
+        <v>0.03777280407032436</v>
       </c>
       <c r="FQ3" t="n">
-        <v>-0.1587444716507308</v>
+        <v>-0.0189004803530027</v>
       </c>
       <c r="FR3" t="n">
         <v>-0</v>
@@ -2093,28 +2093,28 @@
         <v>-0</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0.1451779253046032</v>
+        <v>0.01211388595527601</v>
       </c>
       <c r="FU3" t="n">
         <v>-0</v>
       </c>
       <c r="FV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY3" t="n">
-        <v>-0.05665088541515073</v>
+        <v>0.0181860751058391</v>
       </c>
       <c r="FZ3" t="n">
-        <v>-0.01784186904488137</v>
+        <v>-0.02689565566875902</v>
       </c>
       <c r="GA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB3" t="n">
         <v>-0</v>
@@ -2123,7 +2123,7 @@
         <v>0</v>
       </c>
       <c r="GD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE3" t="n">
         <v>-0</v>
@@ -2132,24 +2132,24 @@
         <v>-0</v>
       </c>
       <c r="GG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.3768651029863613</v>
+        <v>0.4164547641810594</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1417436705556258</v>
+        <v>-0.2506860286442741</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.04791807035791355</v>
+        <v>-0.1175399849933211</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -2161,22 +2161,22 @@
         <v>-0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2791615302444458</v>
+        <v>0.3711386814039132</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1546375200080911</v>
+        <v>-0.3747517414346814</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.09226351554115622</v>
+        <v>-0.187055083519931</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -2194,49 +2194,49 @@
         <v>-0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1316608695916552</v>
+        <v>0.1847802528612869</v>
       </c>
       <c r="U4" t="n">
         <v>-0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.01232264611138479</v>
+        <v>-0.01717312346095936</v>
       </c>
       <c r="W4" t="n">
-        <v>0.04495554595828485</v>
+        <v>-0.008210063504776734</v>
       </c>
       <c r="X4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.07254097510865974</v>
+        <v>0.03490891635550358</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.001875186431800488</v>
+        <v>-0.1410067010177044</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.04650790164479725</v>
+        <v>0.0183640421429273</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>-0</v>
@@ -2245,73 +2245,73 @@
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.0620122028722435</v>
+        <v>0.2686718719330138</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0.09560605680752372</v>
+        <v>-0.0289040531044703</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.008949759057259307</v>
+        <v>0.2379238512688519</v>
       </c>
       <c r="AP4" t="n">
         <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
         <v>-0</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.6521738731654921</v>
+        <v>0.7915301785142975</v>
       </c>
       <c r="AV4" t="n">
         <v>-0</v>
       </c>
       <c r="AW4" t="n">
-        <v>-0.06208025065953061</v>
+        <v>-0.3743766265167753</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.1997586201873875</v>
+        <v>-0.2352853410451714</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
         <v>-0</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.05866092368835474</v>
+        <v>-0.05074730773849197</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>-0.09235156840786729</v>
+        <v>-0.04697005628729487</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.2314242093756145</v>
+        <v>-0.08501151210049067</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
@@ -2320,7 +2320,7 @@
         <v>-0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
         <v>0</v>
@@ -2329,22 +2329,22 @@
         <v>-0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.02659286983351843</v>
+        <v>-0.09353567524575417</v>
       </c>
       <c r="BN4" t="n">
         <v>-0</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.1014976763611799</v>
+        <v>0.004356894456637554</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.07348137270071094</v>
+        <v>0.1294413634123874</v>
       </c>
       <c r="BQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
         <v>-0</v>
@@ -2356,43 +2356,43 @@
         <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.3132765253834296</v>
+        <v>0.4847648458875679</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>-0.003259984482405111</v>
+        <v>-0.2423751880953582</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.06072256757120025</v>
+        <v>-0.05849742997226458</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC4" t="n">
         <v>0</v>
       </c>
       <c r="CD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.1374056239031448</v>
+        <v>-0.2786922051947426</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.06700457575504169</v>
+        <v>0.1716311232898274</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.03833203214262049</v>
+        <v>0.04032734224806658</v>
       </c>
       <c r="CI4" t="n">
         <v>-0</v>
@@ -2401,28 +2401,28 @@
         <v>-0</v>
       </c>
       <c r="CK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
         <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>-0.000474545866457351</v>
+        <v>-0.1505191283744008</v>
       </c>
       <c r="CO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>-0.02986861658656246</v>
+        <v>0.05719495513368056</v>
       </c>
       <c r="CQ4" t="n">
-        <v>-0.06708238805942485</v>
+        <v>0.02990321080304889</v>
       </c>
       <c r="CR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS4" t="n">
         <v>-0</v>
@@ -2434,46 +2434,46 @@
         <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.1306561387313052</v>
+        <v>-0.3027901297254874</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.09237459763335161</v>
+        <v>0.182946988329324</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.02729809018321433</v>
+        <v>0.06624568586083937</v>
       </c>
       <c r="DA4" t="n">
         <v>0</v>
       </c>
       <c r="DB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.09153559822646705</v>
+        <v>-0.3895144803304501</v>
       </c>
       <c r="DG4" t="n">
         <v>0</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.1175248220689988</v>
+        <v>0.2585568381206334</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.180920546759538</v>
+        <v>-0.1027711086889896</v>
       </c>
       <c r="DJ4" t="n">
         <v>-0</v>
@@ -2482,7 +2482,7 @@
         <v>-0</v>
       </c>
       <c r="DL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM4" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.1115215020017622</v>
+        <v>-0.07185227464945144</v>
       </c>
       <c r="DP4" t="n">
         <v>-0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0.0042063308341376</v>
+        <v>0.119708413676922</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.00157225425925337</v>
+        <v>-0.1055314785953529</v>
       </c>
       <c r="DS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT4" t="n">
         <v>-0</v>
@@ -2518,43 +2518,43 @@
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>-0.03275804678820403</v>
+        <v>0.1676128531575997</v>
       </c>
       <c r="DY4" t="n">
         <v>0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.01731399737286671</v>
+        <v>0.1116365996348992</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.00191956083616602</v>
+        <v>-0.053057529699591</v>
       </c>
       <c r="EB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF4" t="n">
         <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.1380945157380195</v>
+        <v>-0.2104396013674377</v>
       </c>
       <c r="EH4" t="n">
         <v>0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.06047342840025212</v>
+        <v>0.1414762441690471</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.08054789368917874</v>
+        <v>0.09505465245715453</v>
       </c>
       <c r="EK4" t="n">
         <v>-0</v>
@@ -2563,7 +2563,7 @@
         <v>-0</v>
       </c>
       <c r="EM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN4" t="n">
         <v>-0</v>
@@ -2572,22 +2572,22 @@
         <v>0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.09888589614782954</v>
+        <v>-0.2645382079673601</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.1391404239329576</v>
+        <v>0.1205062038957369</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.1183490155346203</v>
+        <v>0.01866005208376018</v>
       </c>
       <c r="ET4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV4" t="n">
         <v>0</v>
@@ -2599,46 +2599,46 @@
         <v>0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.1375828171381731</v>
+        <v>-0.33031176745994</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.09349855541378128</v>
+        <v>0.2065593125238711</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.05554829510650583</v>
+        <v>0.03254088913682331</v>
       </c>
       <c r="FC4" t="n">
         <v>-0</v>
       </c>
       <c r="FD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
         <v>-0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.06047890613694973</v>
+        <v>-0.1185672052257185</v>
       </c>
       <c r="FI4" t="n">
         <v>-0</v>
       </c>
       <c r="FJ4" t="n">
-        <v>-0.03583693841497618</v>
+        <v>0.005667539193901909</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.007642451483023787</v>
+        <v>0.04383461092861281</v>
       </c>
       <c r="FL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
@@ -2647,22 +2647,22 @@
         <v>-0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-0.0461037119318517</v>
+        <v>-0.2581722414978972</v>
       </c>
       <c r="FR4" t="n">
         <v>-0</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.1403566245127527</v>
+        <v>0.4460631970336783</v>
       </c>
       <c r="FT4" t="n">
-        <v>-0.1674355318989166</v>
+        <v>0.07154357583045831</v>
       </c>
       <c r="FU4" t="n">
         <v>-0</v>
@@ -2671,34 +2671,34 @@
         <v>-0</v>
       </c>
       <c r="FW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX4" t="n">
         <v>0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.01741668304127783</v>
+        <v>-0.2440019684474944</v>
       </c>
       <c r="GA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.05245090065100413</v>
+        <v>0.07967723245000405</v>
       </c>
       <c r="GC4" t="n">
         <v>0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE4" t="n">
         <v>-0</v>
       </c>
       <c r="GF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG4" t="n">
         <v>-0</v>
@@ -2706,22 +2706,22 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1051169439720761</v>
+        <v>0.3845486970633026</v>
       </c>
       <c r="C5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.02630364218801028</v>
+        <v>0.005626776655712104</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.06086743285451458</v>
+        <v>-0.245077234113018</v>
       </c>
       <c r="G5" t="n">
         <v>-0</v>
@@ -2736,7 +2736,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.07217142882420809</v>
+        <v>0.3833712627018082</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -2745,67 +2745,67 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.01838080668985127</v>
+        <v>-0.1291258637992231</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.06808753734219743</v>
+        <v>-0.2606275178090466</v>
       </c>
       <c r="P5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>-0</v>
       </c>
       <c r="R5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02327023711059273</v>
+        <v>-0.06276420485677564</v>
       </c>
       <c r="U5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.02943402421594671</v>
+        <v>-0.1144142020706723</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.005031743620407145</v>
+        <v>-0.1693591158497939</v>
       </c>
       <c r="Y5" t="n">
         <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.03136727672976817</v>
+        <v>0.1868254858005352</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.01230518264811066</v>
+        <v>-0.06965976851666386</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.02016746016131091</v>
+        <v>0.05480803437023758</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>-0</v>
@@ -2817,19 +2817,19 @@
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.01829368755862074</v>
+        <v>0.1385038826084632</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
         <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.005502076358233817</v>
+        <v>0.008813361444168775</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.05235507252370909</v>
+        <v>-0.1727970186520007</v>
       </c>
       <c r="AQ5" t="n">
         <v>-0</v>
@@ -2841,37 +2841,37 @@
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.1390851596206592</v>
+        <v>0.7457621747630063</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
         <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.0226055133538276</v>
+        <v>-0.2870414799305002</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.114245481061411</v>
+        <v>-0.3757796154528242</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.0495148430369864</v>
+        <v>0.110972725176895</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
@@ -2880,16 +2880,16 @@
         <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.04243570617814339</v>
+        <v>0.01966768383972923</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.02788105780946789</v>
+        <v>-0.1605915945373165</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK5" t="n">
         <v>-0</v>
@@ -2898,7 +2898,7 @@
         <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.03681951819216112</v>
+        <v>0.08540923207518837</v>
       </c>
       <c r="BN5" t="n">
         <v>0</v>
@@ -2907,25 +2907,25 @@
         <v>0</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.02096000084954978</v>
+        <v>0.1330571397884918</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.01743837919932245</v>
+        <v>0.1337136710662416</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT5" t="n">
         <v>0</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.06519021488829535</v>
+        <v>0.3011716649440928</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
@@ -2934,10 +2934,10 @@
         <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.007627476344018488</v>
+        <v>-0.1173364485395802</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.03949755225364059</v>
+        <v>-0.3358058599378736</v>
       </c>
       <c r="CA5" t="n">
         <v>-0</v>
@@ -2949,10 +2949,10 @@
         <v>0</v>
       </c>
       <c r="CD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.03575202230532211</v>
+        <v>-0.2701065122666002</v>
       </c>
       <c r="CF5" t="n">
         <v>0</v>
@@ -2961,10 +2961,10 @@
         <v>-0</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.001071568576695632</v>
+        <v>-0.03206986061509483</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.03496542290385492</v>
+        <v>0.2100809401388246</v>
       </c>
       <c r="CJ5" t="n">
         <v>0</v>
@@ -2973,52 +2973,52 @@
         <v>0</v>
       </c>
       <c r="CL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM5" t="n">
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.006447972671062098</v>
+        <v>-0.2024594238051938</v>
       </c>
       <c r="CO5" t="n">
         <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.0008919496881585154</v>
+        <v>0.0448942583680988</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.006130389420402717</v>
+        <v>0.09117610970657518</v>
       </c>
       <c r="CS5" t="n">
         <v>-0</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.02928358957644351</v>
+        <v>-0.2545721143805471</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
         <v>0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.001912239723848311</v>
+        <v>-0.02153156669479236</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.04122177641531671</v>
+        <v>0.1845930900678951</v>
       </c>
       <c r="DB5" t="n">
         <v>-0</v>
@@ -3033,19 +3033,19 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.0290535539783803</v>
+        <v>-0.07891257745329792</v>
       </c>
       <c r="DG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH5" t="n">
         <v>-0</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.05541385440687965</v>
+        <v>-0.1445836697242458</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.01220038137669107</v>
+        <v>0.2023453903691394</v>
       </c>
       <c r="DK5" t="n">
         <v>0</v>
@@ -3054,52 +3054,52 @@
         <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.007695096945637281</v>
+        <v>-0.09207775341290271</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.02470935940232797</v>
+        <v>-0.0270333610756456</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.0148979233751751</v>
+        <v>0.06079772339049424</v>
       </c>
       <c r="DT5" t="n">
         <v>0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW5" t="n">
         <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.0336021625937538</v>
+        <v>0.151969514431753</v>
       </c>
       <c r="DY5" t="n">
         <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.01965205161036728</v>
+        <v>0.02185009469537643</v>
       </c>
       <c r="EB5" t="n">
-        <v>-0.01018587048994618</v>
+        <v>0.06108704345096807</v>
       </c>
       <c r="EC5" t="n">
         <v>-0</v>
@@ -3108,13 +3108,13 @@
         <v>0</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF5" t="n">
         <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.0248443610558537</v>
+        <v>-0.1074784267740651</v>
       </c>
       <c r="EH5" t="n">
         <v>0</v>
@@ -3123,106 +3123,106 @@
         <v>0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.00811321531550659</v>
+        <v>-0.07944054787355298</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.02357626345466603</v>
+        <v>0.2112197720224833</v>
       </c>
       <c r="EL5" t="n">
         <v>-0</v>
       </c>
       <c r="EM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.01910068926254272</v>
+        <v>-0.1538445078355487</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
         <v>0</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.003424349642129036</v>
+        <v>-0.15067328438878</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.01903699198193745</v>
+        <v>0.1519655501847407</v>
       </c>
       <c r="EU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.03081867436946118</v>
+        <v>-0.2683236446139285</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.004562265822116505</v>
+        <v>-0.07728444753590186</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.03866810096563036</v>
+        <v>0.1926517174822833</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
         <v>0</v>
       </c>
       <c r="FF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.02105999908100281</v>
+        <v>-0.1714642630244562</v>
       </c>
       <c r="FI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ5" t="n">
         <v>-0</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.02890405236307995</v>
+        <v>0.08421934297005775</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.03561252606366989</v>
+        <v>0.2104751335495998</v>
       </c>
       <c r="FM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO5" t="n">
         <v>0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.03044581436349723</v>
+        <v>-0.05476624923502538</v>
       </c>
       <c r="FR5" t="n">
         <v>-0</v>
@@ -3231,63 +3231,63 @@
         <v>-0</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.008825865671211705</v>
+        <v>0.08160049648560251</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.002319771574030192</v>
+        <v>0.02640817136144631</v>
       </c>
       <c r="FV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX5" t="n">
         <v>0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.02724484644533567</v>
+        <v>-0.1012442622089045</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
         <v>-0</v>
       </c>
       <c r="GC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0.0221602590275807</v>
+        <v>0.1484209421827091</v>
       </c>
       <c r="GE5" t="n">
         <v>-0</v>
       </c>
       <c r="GF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.3042707644290619</v>
+        <v>0.4598571532335615</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.07362119314090711</v>
+        <v>-0.1674269792228443</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0466748589854107</v>
+        <v>-0.1264077549150787</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -3305,16 +3305,16 @@
         <v>-0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1981510576177229</v>
+        <v>0.3901200368478211</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.07330777652395946</v>
+        <v>-0.2802837644687167</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.06168350203451296</v>
+        <v>-0.1760682359779872</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -3323,28 +3323,28 @@
         <v>-0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1043241771754919</v>
+        <v>0.1692894484205893</v>
       </c>
       <c r="U6" t="n">
         <v>-0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.03447826259812111</v>
+        <v>0.03191661594669487</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.01592649463459137</v>
+        <v>-0.0780383306650454</v>
       </c>
       <c r="X6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
         <v>-0</v>
@@ -3356,25 +3356,25 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.06453902701222959</v>
+        <v>0.0383128541744748</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.01677352325151172</v>
+        <v>-0.1149867331890708</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.05997405073995581</v>
+        <v>-0.09955960245341766</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>-0</v>
@@ -3383,73 +3383,73 @@
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.05178267970155161</v>
+        <v>0.2540066565611926</v>
       </c>
       <c r="AM6" t="n">
         <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.03784362123134891</v>
+        <v>0.02222665920581003</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.05893988218443832</v>
+        <v>0.1018599881005889</v>
       </c>
       <c r="AP6" t="n">
         <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
         <v>-0</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT6" t="n">
         <v>-0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.4713311732314878</v>
+        <v>0.6102128736996753</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.06670279890919643</v>
+        <v>-0.2685183272143709</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.1005402212454046</v>
+        <v>-0.3473334115246782</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.04276349311437044</v>
+        <v>0.0256040032525971</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.06301956739927515</v>
+        <v>-0.1189502656399802</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.157770408761142</v>
+        <v>-0.03984212379814036</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
@@ -3458,7 +3458,7 @@
         <v>-0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
@@ -3467,22 +3467,22 @@
         <v>-0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.0827020275898508</v>
+        <v>-0.03620819325239846</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.08696551424591184</v>
+        <v>0.07896802007587825</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.0986571519536816</v>
+        <v>0.1526777932217947</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS6" t="n">
         <v>-0</v>
@@ -3494,19 +3494,19 @@
         <v>-0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.2166080337102763</v>
+        <v>0.4292690039881413</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.02790056641005637</v>
+        <v>-0.1890760831580972</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.02013444290002642</v>
+        <v>-0.08322129648446483</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA6" t="n">
         <v>-0</v>
@@ -3521,16 +3521,16 @@
         <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.09277812911825302</v>
+        <v>-0.2196720270635917</v>
       </c>
       <c r="CF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.03793374305745948</v>
+        <v>0.2132915970929905</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.02138065767708598</v>
+        <v>0.0292465996669316</v>
       </c>
       <c r="CI6" t="n">
         <v>-0</v>
@@ -3542,25 +3542,25 @@
         <v>0</v>
       </c>
       <c r="CL6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM6" t="n">
         <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.01034767439074022</v>
+        <v>-0.1081317604102272</v>
       </c>
       <c r="CO6" t="n">
         <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0.00364728934338819</v>
+        <v>0.007574339478461457</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.05021888906518973</v>
+        <v>0.01213077953569976</v>
       </c>
       <c r="CR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS6" t="n">
         <v>-0</v>
@@ -3569,22 +3569,22 @@
         <v>-0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.08656085828761993</v>
+        <v>-0.2332291062081981</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.06079648324159766</v>
+        <v>0.2183022214944031</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.02498380381659208</v>
+        <v>0.03966739028126338</v>
       </c>
       <c r="DA6" t="n">
         <v>0</v>
@@ -3596,28 +3596,28 @@
         <v>-0</v>
       </c>
       <c r="DD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.05973365953150885</v>
+        <v>-0.1914828350826818</v>
       </c>
       <c r="DG6" t="n">
         <v>0</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.1772681487929275</v>
+        <v>0.1646311357751472</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.005972508015114465</v>
+        <v>-0.06370831034635945</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL6" t="n">
         <v>0</v>
@@ -3629,19 +3629,19 @@
         <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.06108286784308737</v>
+        <v>-0.1547350807705175</v>
       </c>
       <c r="DP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0.03605619658539891</v>
+        <v>0.1128664515627352</v>
       </c>
       <c r="DR6" t="n">
-        <v>-0.01944629691886687</v>
+        <v>-0.1166222339400662</v>
       </c>
       <c r="DS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT6" t="n">
         <v>-0</v>
@@ -3656,22 +3656,22 @@
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.03243079827949347</v>
+        <v>0.08244197028221971</v>
       </c>
       <c r="DY6" t="n">
         <v>0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.02632346500164758</v>
+        <v>0.1451295005857453</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.0215283276640242</v>
+        <v>-0.1001279226406101</v>
       </c>
       <c r="EB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED6" t="n">
         <v>0</v>
@@ -3683,16 +3683,16 @@
         <v>0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.07381460696470696</v>
+        <v>-0.1334420752105529</v>
       </c>
       <c r="EH6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI6" t="n">
-        <v>-0.09704953611469477</v>
+        <v>-0.2789589152334713</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.03617192383735601</v>
+        <v>0.04021449387191568</v>
       </c>
       <c r="EK6" t="n">
         <v>-0</v>
@@ -3701,7 +3701,7 @@
         <v>-0</v>
       </c>
       <c r="EM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN6" t="n">
         <v>-0</v>
@@ -3710,22 +3710,22 @@
         <v>0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.07747707360405898</v>
+        <v>-0.1871394912063507</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.06778398253600923</v>
+        <v>0.1212281305029272</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.03046137392336283</v>
+        <v>-0.03919930273880585</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV6" t="n">
         <v>0</v>
@@ -3734,19 +3734,19 @@
         <v>-0</v>
       </c>
       <c r="EX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.08440747114714456</v>
+        <v>-0.2588448996441237</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.064021921552877</v>
+        <v>0.225497197457569</v>
       </c>
       <c r="FB6" t="n">
-        <v>-0.02901897394015685</v>
+        <v>0.01966997730720977</v>
       </c>
       <c r="FC6" t="n">
         <v>-0</v>
@@ -3758,49 +3758,49 @@
         <v>0</v>
       </c>
       <c r="FF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG6" t="n">
         <v>-0</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.01354057686936464</v>
+        <v>-0.0511569416714935</v>
       </c>
       <c r="FI6" t="n">
         <v>-0</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.02457309375588753</v>
+        <v>-0.0761118516607969</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.02637045483412469</v>
+        <v>0.0723806613534468</v>
       </c>
       <c r="FL6" t="n">
         <v>-0</v>
       </c>
       <c r="FM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN6" t="n">
         <v>-0</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.004034215224279803</v>
+        <v>-0.1287700779902726</v>
       </c>
       <c r="FR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.02210354471164704</v>
+        <v>0.3684632953563796</v>
       </c>
       <c r="FT6" t="n">
-        <v>-0.04422319433200764</v>
+        <v>0.1264654894932553</v>
       </c>
       <c r="FU6" t="n">
         <v>-0</v>
@@ -3815,28 +3815,28 @@
         <v>0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.02173643692214608</v>
+        <v>-0.1872221754006652</v>
       </c>
       <c r="GA6" t="n">
         <v>-0</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.01958807388461127</v>
+        <v>0.09319539621716946</v>
       </c>
       <c r="GC6" t="n">
         <v>0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE6" t="n">
         <v>-0</v>
       </c>
       <c r="GF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG6" t="n">
         <v>-0</v>
@@ -3844,133 +3844,133 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-0.05118991298359994</v>
+        <v>-0.1827758031758365</v>
       </c>
       <c r="B7" t="n">
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1469885633023001</v>
+        <v>0.1390908002087107</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1231281601628096</v>
+        <v>-0.124364459892416</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.01347329364292025</v>
+        <v>0.01173306607444656</v>
       </c>
       <c r="H7" t="n">
         <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.007056576865615135</v>
+        <v>-0.179201287512659</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08146765204385442</v>
+        <v>0.07726542390548832</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.05098032179043735</v>
+        <v>-0.2100109793272501</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.01352728260668758</v>
+        <v>0.02374876534219449</v>
       </c>
       <c r="Q7" t="n">
         <v>-0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.04402320495414067</v>
+        <v>0.0292541609724791</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.08625251493935714</v>
+        <v>-0.03550957376513707</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.04407036176842356</v>
+        <v>-0.1085220101742465</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.06417624994048053</v>
+        <v>0.02500784303417157</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.0377597367933551</v>
+        <v>0.1411880635832199</v>
       </c>
       <c r="AC7" t="n">
         <v>-0</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.05028961470073901</v>
+        <v>-0.1160233195515507</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.053960720465996</v>
+        <v>-0.2288980560799042</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.0087319110121823</v>
+        <v>0.03339809266839804</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.01761367657753091</v>
+        <v>0.02717497886616967</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.04704672009957166</v>
+        <v>-0.08578399822308704</v>
       </c>
       <c r="AN7" t="n">
         <v>-0</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.008955031074869889</v>
+        <v>-0.03293517272487818</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.00489066723303997</v>
+        <v>0.02213366197647604</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -3979,79 +3979,79 @@
         <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0.05330756086056512</v>
+        <v>-0.1361379215875134</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.2256840020167878</v>
+        <v>0.08095647421919273</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.3781435591038386</v>
+        <v>-0.3000690870362944</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.03809513304606111</v>
+        <v>0.03772325019616372</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>-0.09691764698108589</v>
+        <v>-0.05910336869072866</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.002491549676982871</v>
+        <v>-0.00499822043699082</v>
       </c>
       <c r="BF7" t="n">
         <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.02617058404159672</v>
+        <v>0.1105530474447658</v>
       </c>
       <c r="BH7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0.01011700695834824</v>
+        <v>-0.07432621292798114</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
         <v>0</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0.01650744444809136</v>
+        <v>0.1144390916815008</v>
       </c>
       <c r="BM7" t="n">
         <v>-0</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.1189234339255871</v>
+        <v>0.0678303720994453</v>
       </c>
       <c r="BO7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.03608052620561101</v>
+        <v>0.07151471013427257</v>
       </c>
       <c r="BQ7" t="n">
         <v>-0</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.03373888406575386</v>
+        <v>0.02228142327337222</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
@@ -4060,25 +4060,25 @@
         <v>-0</v>
       </c>
       <c r="BU7" t="n">
-        <v>-0.01674677244690163</v>
+        <v>-0.06945756812202269</v>
       </c>
       <c r="BV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.05991752291653291</v>
+        <v>0.1009366028913705</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.2046084357509654</v>
+        <v>-0.155825230925177</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>-0.02916907870838012</v>
+        <v>0.05213922498640262</v>
       </c>
       <c r="CB7" t="n">
         <v>-0</v>
@@ -4087,187 +4087,187 @@
         <v>-0</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.04005673079207914</v>
+        <v>0.08293984331326877</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CF7" t="n">
-        <v>-0.04956729459799291</v>
+        <v>0.01288850175463451</v>
       </c>
       <c r="CG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.04611814493292187</v>
+        <v>0.1001149569681377</v>
       </c>
       <c r="CI7" t="n">
         <v>0</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.01109706262177574</v>
+        <v>0.009435908858916481</v>
       </c>
       <c r="CK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.02130084135118367</v>
+        <v>-0.05207636248845111</v>
       </c>
       <c r="CN7" t="n">
         <v>0</v>
       </c>
       <c r="CO7" t="n">
-        <v>-0.003248509268305323</v>
+        <v>0.02744209034851366</v>
       </c>
       <c r="CP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.06339741083108948</v>
+        <v>-0.02960337841421428</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
-        <v>-0.0007872060787891004</v>
+        <v>0.006453779326619147</v>
       </c>
       <c r="CT7" t="n">
         <v>0</v>
       </c>
       <c r="CU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.02345174518351624</v>
+        <v>0.08584951890885761</v>
       </c>
       <c r="CW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0.04404338264379898</v>
+        <v>-0.04144812657984906</v>
       </c>
       <c r="CY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.01836096579459469</v>
+        <v>0.05301921135324145</v>
       </c>
       <c r="DA7" t="n">
         <v>-0</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.01919322668161283</v>
+        <v>0.02210891829042782</v>
       </c>
       <c r="DC7" t="n">
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.04147713870083898</v>
+        <v>-0.05006200410162402</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG7" t="n">
-        <v>-0.06317427760417384</v>
+        <v>-0.03404916519976465</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.03203511346705304</v>
+        <v>0.2169398786099627</v>
       </c>
       <c r="DJ7" t="n">
         <v>0</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.02499595073601978</v>
+        <v>-0.04067624116366625</v>
       </c>
       <c r="DL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM7" t="n">
         <v>-0</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.06446234131134129</v>
+        <v>-0.08921016180402352</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.0154846355365038</v>
+        <v>0.03402775305800194</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.0008577835500698698</v>
+        <v>-0.216404796013847</v>
       </c>
       <c r="DS7" t="n">
         <v>0</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.04883999716597362</v>
+        <v>-0.01263053744864007</v>
       </c>
       <c r="DU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW7" t="n">
-        <v>-0.01467909883563562</v>
+        <v>0.007918133123864867</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DY7" t="n">
-        <v>-0.005586738112637026</v>
+        <v>0.1507426248659957</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.06983158720646049</v>
+        <v>-0.2545360711860413</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
-        <v>-0.005113909899916519</v>
+        <v>-0.05136647317269526</v>
       </c>
       <c r="ED7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.008874634974052581</v>
+        <v>0.07346002790951023</v>
       </c>
       <c r="EG7" t="n">
         <v>0</v>
       </c>
       <c r="EH7" t="n">
-        <v>-0.1140283674980352</v>
+        <v>0.01268532962330607</v>
       </c>
       <c r="EI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>-0.02043255180536351</v>
+        <v>0.04469932176715764</v>
       </c>
       <c r="EK7" t="n">
         <v>-0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0.01125056757076988</v>
+        <v>0.1056217002555701</v>
       </c>
       <c r="EM7" t="n">
         <v>-0</v>
@@ -4276,79 +4276,79 @@
         <v>-0</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.02144852175120368</v>
+        <v>0.08156594411843281</v>
       </c>
       <c r="EP7" t="n">
         <v>0</v>
       </c>
       <c r="EQ7" t="n">
-        <v>-0.02588885618474144</v>
+        <v>0.08228177336059836</v>
       </c>
       <c r="ER7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.08873783866833607</v>
+        <v>0.04172925262796739</v>
       </c>
       <c r="ET7" t="n">
         <v>0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0.03120313310343639</v>
+        <v>0.06943529564012763</v>
       </c>
       <c r="EV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW7" t="n">
         <v>-0</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.02395580516880035</v>
+        <v>0.087138094895075</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EZ7" t="n">
-        <v>-0.0438148718815022</v>
+        <v>-0.04520651781439215</v>
       </c>
       <c r="FA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.03546362150033653</v>
+        <v>0.08397748284787705</v>
       </c>
       <c r="FC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.01374150559081772</v>
+        <v>0.003231048122523074</v>
       </c>
       <c r="FE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.01482098000407318</v>
+        <v>0.3469821270888144</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FI7" t="n">
-        <v>-0.02407139850298252</v>
+        <v>0.005298625482073544</v>
       </c>
       <c r="FJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.009887836490667126</v>
+        <v>0.0584474585147745</v>
       </c>
       <c r="FL7" t="n">
         <v>-0</v>
       </c>
       <c r="FM7" t="n">
-        <v>-0.03655992695781329</v>
+        <v>0.01803049509977602</v>
       </c>
       <c r="FN7" t="n">
         <v>0</v>
@@ -4357,40 +4357,40 @@
         <v>0</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.04392107171414205</v>
+        <v>0.3068787181990405</v>
       </c>
       <c r="FQ7" t="n">
         <v>0</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.05406563567787868</v>
+        <v>-0.2123633306535887</v>
       </c>
       <c r="FS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT7" t="n">
-        <v>-0.06817784977113517</v>
+        <v>0.1245257890479915</v>
       </c>
       <c r="FU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV7" t="n">
-        <v>-0.0155992543219893</v>
+        <v>0.0004753827869210024</v>
       </c>
       <c r="FW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0.01546254903695856</v>
+        <v>0.1630748232465781</v>
       </c>
       <c r="FZ7" t="n">
         <v>-0</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.04387646811632798</v>
+        <v>-0.0014469141144572</v>
       </c>
       <c r="GB7" t="n">
         <v>-0</v>
@@ -4399,39 +4399,39 @@
         <v>-0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
-        <v>-0.02675044364630135</v>
+        <v>0.09197607963895044</v>
       </c>
       <c r="GF7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1151413771141204</v>
+        <v>0.5792347897385997</v>
       </c>
       <c r="C8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.02120139248682431</v>
+        <v>0.005641612988537063</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.06558931277076671</v>
+        <v>-0.3179233609944637</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H8" t="n">
         <v>-0</v>
@@ -4443,7 +4443,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.08891877070331128</v>
+        <v>0.622059746814416</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -4452,70 +4452,70 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.01353664439151244</v>
+        <v>-0.1493763004570866</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.05050756433884802</v>
+        <v>-0.2632718632669277</v>
       </c>
       <c r="P8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>-0</v>
       </c>
       <c r="R8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01570704366422641</v>
+        <v>0.1173174554300806</v>
       </c>
       <c r="U8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.01812590675292399</v>
+        <v>-0.09144083432960685</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.01195286350996526</v>
+        <v>-0.1107776669459889</v>
       </c>
       <c r="Y8" t="n">
         <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.02606639399473628</v>
+        <v>0.1210841122951058</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.01730151175573778</v>
+        <v>-0.2059371346587808</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.01391333726444061</v>
+        <v>-0.02919536431983764</v>
       </c>
       <c r="AH8" t="n">
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ8" t="n">
         <v>-0</v>
@@ -4524,22 +4524,22 @@
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.01590904403987716</v>
+        <v>0.2281048483426079</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
         <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.006747971784900173</v>
+        <v>0.0398759757589347</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.04280989905658528</v>
+        <v>-0.1962219774546726</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR8" t="n">
         <v>-0</v>
@@ -4548,10 +4548,10 @@
         <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.1149826688623442</v>
+        <v>1.014671344012539</v>
       </c>
       <c r="AV8" t="n">
         <v>-0</v>
@@ -4560,25 +4560,25 @@
         <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.001860238164710814</v>
+        <v>-0.3384262808494439</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0.07291621389837066</v>
+        <v>-0.3031726228401566</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC8" t="n">
         <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.05956902068953607</v>
+        <v>-0.01587353303689929</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
@@ -4587,52 +4587,52 @@
         <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.04338051758004723</v>
+        <v>-0.06089888974192193</v>
       </c>
       <c r="BH8" t="n">
-        <v>-0.0335973037551742</v>
+        <v>-0.2306258897408705</v>
       </c>
       <c r="BI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK8" t="n">
         <v>-0</v>
       </c>
       <c r="BL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.03578817825354798</v>
+        <v>0.1535659848356476</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.01544988250728137</v>
+        <v>0.156893510820557</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.007871300447666388</v>
+        <v>0.07642807942427438</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.05039962179909811</v>
+        <v>0.5266790250764515</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
@@ -4641,13 +4641,13 @@
         <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>-0.002616841521859171</v>
+        <v>-0.09879354530196781</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0.03198513724282698</v>
+        <v>-0.2733133946779864</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB8" t="n">
         <v>-0</v>
@@ -4656,25 +4656,25 @@
         <v>0</v>
       </c>
       <c r="CD8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.02967913584225957</v>
+        <v>-0.3014674995783492</v>
       </c>
       <c r="CF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG8" t="n">
         <v>-0</v>
       </c>
       <c r="CH8" t="n">
-        <v>-0.0001587528934366263</v>
+        <v>0.02073896731028723</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.02261371020006894</v>
+        <v>0.2035229107523766</v>
       </c>
       <c r="CJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK8" t="n">
         <v>0</v>
@@ -4686,22 +4686,22 @@
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0.006564496096210115</v>
+        <v>-0.2195119578931587</v>
       </c>
       <c r="CO8" t="n">
         <v>-0</v>
       </c>
       <c r="CP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ8" t="n">
-        <v>1.030969939519064e-05</v>
+        <v>0.1065409288920307</v>
       </c>
       <c r="CR8" t="n">
-        <v>-0.007713461943026364</v>
+        <v>0.0933624929919256</v>
       </c>
       <c r="CS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT8" t="n">
         <v>0</v>
@@ -4710,25 +4710,25 @@
         <v>0</v>
       </c>
       <c r="CV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.02551195413798963</v>
+        <v>-0.2862621191276723</v>
       </c>
       <c r="CX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY8" t="n">
         <v>0</v>
       </c>
       <c r="CZ8" t="n">
-        <v>-0.001848252682189893</v>
+        <v>-0.01029879154469985</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.02616333304832254</v>
+        <v>0.1938174143528437</v>
       </c>
       <c r="DB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC8" t="n">
         <v>-0</v>
@@ -4740,19 +4740,19 @@
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.006884282973123075</v>
+        <v>-0.05779726660840227</v>
       </c>
       <c r="DG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH8" t="n">
         <v>-0</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.01313633905673768</v>
+        <v>-0.0786674844724871</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.02139054712761548</v>
+        <v>0.04913054893841456</v>
       </c>
       <c r="DK8" t="n">
         <v>0</v>
@@ -4761,25 +4761,25 @@
         <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN8" t="n">
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.006661208130874914</v>
+        <v>-0.1156296724738008</v>
       </c>
       <c r="DP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.03178975754312756</v>
+        <v>-0.05177290863465791</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.001513707066423937</v>
+        <v>0.1165533241253972</v>
       </c>
       <c r="DT8" t="n">
         <v>0</v>
@@ -4794,46 +4794,46 @@
         <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.02857708390799611</v>
+        <v>0.0889092889965003</v>
       </c>
       <c r="DY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ8" t="n">
         <v>0</v>
       </c>
       <c r="EA8" t="n">
-        <v>-0.02507751086127255</v>
+        <v>-0.003666063124909253</v>
       </c>
       <c r="EB8" t="n">
-        <v>-0.002528650497869477</v>
+        <v>-0.07112532116250397</v>
       </c>
       <c r="EC8" t="n">
         <v>-0</v>
       </c>
       <c r="ED8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF8" t="n">
         <v>0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.02277071148351542</v>
+        <v>-0.08804750836363798</v>
       </c>
       <c r="EH8" t="n">
         <v>0</v>
       </c>
       <c r="EI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.004612832404248091</v>
+        <v>-0.116223743306053</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.01001535769124873</v>
+        <v>0.1281073286443874</v>
       </c>
       <c r="EL8" t="n">
         <v>-0</v>
@@ -4842,67 +4842,67 @@
         <v>-0</v>
       </c>
       <c r="EN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO8" t="n">
         <v>0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.0223582288680257</v>
+        <v>-0.1987754951819361</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER8" t="n">
         <v>-0</v>
       </c>
       <c r="ES8" t="n">
-        <v>-0.01780617162037657</v>
+        <v>-0.06384965319710494</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.02121264387893909</v>
+        <v>0.06416823891623624</v>
       </c>
       <c r="EU8" t="n">
         <v>0</v>
       </c>
       <c r="EV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW8" t="n">
         <v>0</v>
       </c>
       <c r="EX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.02793710856872804</v>
+        <v>-0.3176281618521316</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.00360363606376792</v>
+        <v>-0.03004476727998318</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.02723253543047682</v>
+        <v>0.1773724617441343</v>
       </c>
       <c r="FD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE8" t="n">
         <v>0</v>
       </c>
       <c r="FF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH8" t="n">
-        <v>-0.008731456033408361</v>
+        <v>-0.2672218380951679</v>
       </c>
       <c r="FI8" t="n">
         <v>0</v>
@@ -4911,13 +4911,13 @@
         <v>-0</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.02978871355693611</v>
+        <v>0.134869545945567</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.03035277838727529</v>
+        <v>0.171053738809288</v>
       </c>
       <c r="FM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN8" t="n">
         <v>0</v>
@@ -4926,10 +4926,10 @@
         <v>0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>-0.01278100126120738</v>
+        <v>-0.1370115948678457</v>
       </c>
       <c r="FR8" t="n">
         <v>-0</v>
@@ -4938,43 +4938,43 @@
         <v>-0</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.004592579554200098</v>
+        <v>0.04693402605916082</v>
       </c>
       <c r="FU8" t="n">
-        <v>-0.0009844319960940291</v>
+        <v>-0.007017752270225413</v>
       </c>
       <c r="FV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>-0.0223710357862876</v>
+        <v>-0.1309743623197425</v>
       </c>
       <c r="GA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB8" t="n">
         <v>-0</v>
       </c>
       <c r="GC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0.02556245511404613</v>
+        <v>0.02480514966925675</v>
       </c>
       <c r="GE8" t="n">
         <v>-0</v>
       </c>
       <c r="GF8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG8" t="n">
         <v>0</v>
@@ -4985,43 +4985,43 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4091614561486824</v>
+        <v>0.308996468525669</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1734949913805842</v>
+        <v>-0.3405658207457207</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1186385829863308</v>
+        <v>0.02599819074638254</v>
       </c>
       <c r="F9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>-0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.361799473659103</v>
+        <v>0.3271362834774912</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1300000103149771</v>
+        <v>-0.3236729440751789</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1318555270535784</v>
+        <v>0.01693220675831697</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -5039,19 +5039,19 @@
         <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.09858053701486691</v>
+        <v>0.0780716446883348</v>
       </c>
       <c r="U9" t="n">
         <v>-0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.003068964045829131</v>
+        <v>-0.02998579408554568</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1154843903217675</v>
+        <v>-0.2079501898875449</v>
       </c>
       <c r="X9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>-0</v>
@@ -5063,25 +5063,25 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.1818891711156737</v>
+        <v>0.01254847845893134</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.009097434831107401</v>
+        <v>-0.1432227917528575</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.01787610290243019</v>
+        <v>-0.1223642974292732</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>-0</v>
@@ -5090,46 +5090,46 @@
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.005018298973233959</v>
+        <v>0.1697383738037656</v>
       </c>
       <c r="AM9" t="n">
         <v>-0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.07326471399819452</v>
+        <v>-0.09046082952703348</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.09646414510768525</v>
+        <v>0.02903805867044135</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
         <v>-0</v>
       </c>
       <c r="AS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
         <v>-0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.5284204718148419</v>
+        <v>0.3949266821790538</v>
       </c>
       <c r="AV9" t="n">
         <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0.0621730717163007</v>
+        <v>-0.1666235619840896</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.03479496378158545</v>
+        <v>-0.3507869035896049</v>
       </c>
       <c r="AY9" t="n">
         <v>-0</v>
@@ -5144,19 +5144,19 @@
         <v>-0</v>
       </c>
       <c r="BC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.1026795702989242</v>
+        <v>-0.06187383324427942</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.06715918547852349</v>
+        <v>-0.09375331080421262</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.09072006103730652</v>
+        <v>-0.03487304585123391</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
@@ -5174,16 +5174,16 @@
         <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.1186381420303434</v>
+        <v>0.01019271761691148</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.06055921836782494</v>
+        <v>0.1011310893543693</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.188642350580389</v>
+        <v>0.08489047040005643</v>
       </c>
       <c r="BQ9" t="n">
         <v>-0</v>
@@ -5201,49 +5201,49 @@
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.2707257239178433</v>
+        <v>0.254970888804496</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX9" t="n">
-        <v>-0.02386755071592481</v>
+        <v>-0.1435495928129284</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.08764477553535285</v>
+        <v>-0.07957198860725977</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB9" t="n">
         <v>0</v>
       </c>
       <c r="CC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD9" t="n">
         <v>0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.1061942122682814</v>
+        <v>-0.1688761721258076</v>
       </c>
       <c r="CF9" t="n">
         <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.02487318704251809</v>
+        <v>0.2371227021943568</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.02059349374645128</v>
+        <v>0.0293327441367428</v>
       </c>
       <c r="CI9" t="n">
         <v>0</v>
       </c>
       <c r="CJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK9" t="n">
         <v>0</v>
@@ -5255,52 +5255,52 @@
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.07321481611807398</v>
+        <v>-0.03172468274859303</v>
       </c>
       <c r="CO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.07926161489219861</v>
+        <v>0.3928365451543803</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.09757538109585465</v>
+        <v>0.1045567860115483</v>
       </c>
       <c r="CR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU9" t="n">
         <v>-0</v>
       </c>
       <c r="CV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.09390305464675039</v>
+        <v>-0.1453478017070817</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.04304923059919739</v>
+        <v>0.246705163816555</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.01363011959130935</v>
+        <v>0.03353949631472369</v>
       </c>
       <c r="DA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD9" t="n">
         <v>0</v>
@@ -5309,43 +5309,43 @@
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.004621941285315018</v>
+        <v>0.0185312556534118</v>
       </c>
       <c r="DG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.1426186363236022</v>
+        <v>0.09298306615825065</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.01032161890431729</v>
+        <v>-0.03707920391405937</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL9" t="n">
         <v>0</v>
       </c>
       <c r="DM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.1066599446398987</v>
+        <v>-0.1467721117726908</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0.093421243279827</v>
+        <v>0.1813028915778994</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.08506522004439747</v>
+        <v>0.01463507183589489</v>
       </c>
       <c r="DS9" t="n">
         <v>-0</v>
@@ -5357,22 +5357,22 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>-0.1405125896851269</v>
+        <v>-0.116255280206534</v>
       </c>
       <c r="DY9" t="n">
         <v>-0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>-0.03086096900861132</v>
+        <v>-0.1430657833613841</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.06826028997202199</v>
+        <v>-0.1736268217106606</v>
       </c>
       <c r="EB9" t="n">
         <v>0</v>
@@ -5381,34 +5381,34 @@
         <v>0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
         <v>-0</v>
       </c>
       <c r="EF9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.1071472712616378</v>
+        <v>-0.05010518442173056</v>
       </c>
       <c r="EH9" t="n">
         <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.09590680339235111</v>
+        <v>0.1560411497214809</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.1568919321323304</v>
+        <v>0.0610640782933412</v>
       </c>
       <c r="EK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL9" t="n">
         <v>-0</v>
       </c>
       <c r="EM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN9" t="n">
         <v>-0</v>
@@ -5417,43 +5417,43 @@
         <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.1014054075897077</v>
+        <v>-0.1404079854352149</v>
       </c>
       <c r="EQ9" t="n">
         <v>0</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.03622350257617934</v>
+        <v>0.1414249136692763</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.07205896457158327</v>
+        <v>-0.02674375898493277</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU9" t="n">
         <v>0</v>
       </c>
       <c r="EV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX9" t="n">
         <v>0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.09336597668776314</v>
+        <v>-0.1683036753702467</v>
       </c>
       <c r="EZ9" t="n">
         <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.04864282819406354</v>
+        <v>0.2585833866029332</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.03245457534086011</v>
+        <v>0.006564023484895351</v>
       </c>
       <c r="FC9" t="n">
         <v>-0</v>
@@ -5462,25 +5462,25 @@
         <v>0</v>
       </c>
       <c r="FE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF9" t="n">
         <v>-0</v>
       </c>
       <c r="FG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0.1670924351741474</v>
+        <v>-0.08302431167073943</v>
       </c>
       <c r="FI9" t="n">
         <v>0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.05921114333078573</v>
+        <v>0.1088468036620794</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.08168475969922134</v>
+        <v>-0.2118118019317137</v>
       </c>
       <c r="FL9" t="n">
         <v>-0</v>
@@ -5489,25 +5489,25 @@
         <v>-0</v>
       </c>
       <c r="FN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO9" t="n">
         <v>0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.02169336797727455</v>
+        <v>-0.02648381642412006</v>
       </c>
       <c r="FR9" t="n">
         <v>-0</v>
       </c>
       <c r="FS9" t="n">
-        <v>-0.02987002061603938</v>
+        <v>-0.03774587794188477</v>
       </c>
       <c r="FT9" t="n">
-        <v>-0.07056283894876543</v>
+        <v>0.0778227626556808</v>
       </c>
       <c r="FU9" t="n">
         <v>0</v>
@@ -5516,22 +5516,22 @@
         <v>0</v>
       </c>
       <c r="FW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX9" t="n">
         <v>0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.06276636343257126</v>
+        <v>-0.08901848901058587</v>
       </c>
       <c r="GA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB9" t="n">
-        <v>-0.04588437840883633</v>
+        <v>0.2425498988348335</v>
       </c>
       <c r="GC9" t="n">
         <v>-0</v>
@@ -5543,15 +5543,15 @@
         <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.1583835024169755</v>
+        <v>0.1179213036002479</v>
       </c>
       <c r="B10" t="n">
         <v>0</v>
@@ -5560,25 +5560,25 @@
         <v>-0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1139641104287337</v>
+        <v>-0.2131714120443099</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1009380592462036</v>
+        <v>0.06872224224991041</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1551006367069048</v>
+        <v>0.07717209249885583</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -5587,25 +5587,25 @@
         <v>-0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.03857486829405607</v>
+        <v>-0.2663296869712399</v>
       </c>
       <c r="N10" t="n">
-        <v>0.04574928931950936</v>
+        <v>0.02004079313459674</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.03267710098174131</v>
+        <v>-0.02734562740827572</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -5614,40 +5614,40 @@
         <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0781174571504257</v>
+        <v>-0.04728515434275252</v>
       </c>
       <c r="W10" t="n">
-        <v>0.05526430878946224</v>
+        <v>-0.05628796656870198</v>
       </c>
       <c r="X10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>-0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA10" t="n">
         <v>-0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.02970045296882918</v>
+        <v>0.03695107066640502</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.02582139569676667</v>
+        <v>0.06295986141272965</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.01311990168898066</v>
+        <v>0.1852895677428929</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH10" t="n">
         <v>0</v>
@@ -5656,49 +5656,49 @@
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>-0.01578264178609782</v>
+        <v>0.02829593424152057</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.01654878097590401</v>
+        <v>-0.1430797601433728</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.05956368669679393</v>
+        <v>0.05383052507153074</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS10" t="n">
         <v>-0</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.1175392525304826</v>
+        <v>-0.07331697344973107</v>
       </c>
       <c r="AU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>-0.07697902751771067</v>
+        <v>-0.3489956596825249</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.1760160525265058</v>
+        <v>-0.009623800910085443</v>
       </c>
       <c r="AY10" t="n">
         <v>-0</v>
@@ -5713,7 +5713,7 @@
         <v>-0</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.1333765281423735</v>
+        <v>0.1694184107104574</v>
       </c>
       <c r="BD10" t="n">
         <v>0</v>
@@ -5722,37 +5722,37 @@
         <v>-0</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.008449796618625783</v>
+        <v>0.2210932088726231</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.06277701883467784</v>
+        <v>0.1674611212745722</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
       </c>
       <c r="BI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK10" t="n">
         <v>0</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.06126642720622404</v>
+        <v>-0.002463702225850822</v>
       </c>
       <c r="BM10" t="n">
         <v>0</v>
       </c>
       <c r="BN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.01622996226704749</v>
+        <v>0.01329209329784438</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.1189231193507078</v>
+        <v>-0.1085048070035848</v>
       </c>
       <c r="BQ10" t="n">
         <v>0</v>
@@ -5761,25 +5761,25 @@
         <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.05379697549844561</v>
+        <v>-0.06312329594936843</v>
       </c>
       <c r="BV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW10" t="n">
         <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>-0.006746651188505628</v>
+        <v>-0.2332707122402755</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.08336343750006825</v>
+        <v>-0.04421461473312124</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -5788,13 +5788,13 @@
         <v>0</v>
       </c>
       <c r="CB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD10" t="n">
-        <v>-0.03279158314006766</v>
+        <v>-0.05270632364384337</v>
       </c>
       <c r="CE10" t="n">
         <v>0</v>
@@ -5803,16 +5803,16 @@
         <v>0</v>
       </c>
       <c r="CG10" t="n">
-        <v>-0.01672298739036377</v>
+        <v>0.1023079837622673</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.02763330252587589</v>
+        <v>-0.02234714846545557</v>
       </c>
       <c r="CI10" t="n">
         <v>0</v>
       </c>
       <c r="CJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK10" t="n">
         <v>0</v>
@@ -5821,34 +5821,34 @@
         <v>-0</v>
       </c>
       <c r="CM10" t="n">
-        <v>-0.02866847214034872</v>
+        <v>-0.001011420642045905</v>
       </c>
       <c r="CN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO10" t="n">
         <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>-0.07399570793638176</v>
+        <v>0.09203815941999674</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.06642034648428444</v>
+        <v>-0.04480288930826942</v>
       </c>
       <c r="CR10" t="n">
         <v>0</v>
       </c>
       <c r="CS10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU10" t="n">
         <v>-0</v>
       </c>
       <c r="CV10" t="n">
-        <v>-0.0199337549448568</v>
+        <v>-0.04559017287968824</v>
       </c>
       <c r="CW10" t="n">
         <v>-0</v>
@@ -5857,10 +5857,10 @@
         <v>-0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.0008653100213300115</v>
+        <v>0.1026124503526847</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.01705840111616728</v>
+        <v>-0.005084954325718478</v>
       </c>
       <c r="DA10" t="n">
         <v>-0</v>
@@ -5872,10 +5872,10 @@
         <v>-0</v>
       </c>
       <c r="DD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE10" t="n">
-        <v>-0.01481795541245693</v>
+        <v>-0.001164995521216487</v>
       </c>
       <c r="DF10" t="n">
         <v>-0</v>
@@ -5884,10 +5884,10 @@
         <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.0820391047358866</v>
+        <v>0.08408199878222058</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.03632029547514213</v>
+        <v>-0.0197437210478163</v>
       </c>
       <c r="DJ10" t="n">
         <v>0</v>
@@ -5902,7 +5902,7 @@
         <v>0</v>
       </c>
       <c r="DN10" t="n">
-        <v>-0.02961216689888443</v>
+        <v>-0.07038661152348044</v>
       </c>
       <c r="DO10" t="n">
         <v>-0</v>
@@ -5911,70 +5911,70 @@
         <v>0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.05291861596222491</v>
+        <v>0.01794172612813475</v>
       </c>
       <c r="DR10" t="n">
-        <v>-0.07381534476504507</v>
+        <v>0.005533359020620751</v>
       </c>
       <c r="DS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV10" t="n">
         <v>0</v>
       </c>
       <c r="DW10" t="n">
-        <v>-0.04304649770344393</v>
+        <v>0.01765472738120363</v>
       </c>
       <c r="DX10" t="n">
         <v>-0</v>
       </c>
       <c r="DY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>-0.02524261140260131</v>
+        <v>0.002958391517935371</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.04366498930361729</v>
+        <v>0.02046902012474408</v>
       </c>
       <c r="EB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>-0.02437795559924612</v>
+        <v>-0.07965725415702797</v>
       </c>
       <c r="EG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH10" t="n">
         <v>0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.01917060298548851</v>
+        <v>0.0936666261241889</v>
       </c>
       <c r="EJ10" t="n">
-        <v>-0.002351181141491149</v>
+        <v>0.02408669355429358</v>
       </c>
       <c r="EK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM10" t="n">
         <v>0</v>
@@ -5983,22 +5983,22 @@
         <v>-0</v>
       </c>
       <c r="EO10" t="n">
-        <v>-0.005323942783940798</v>
+        <v>0.03266867327276353</v>
       </c>
       <c r="EP10" t="n">
         <v>0</v>
       </c>
       <c r="EQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.02301252865372973</v>
+        <v>0.1192900303275084</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.01726965172718538</v>
+        <v>0.02032865920888527</v>
       </c>
       <c r="ET10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU10" t="n">
         <v>0</v>
@@ -6010,19 +6010,19 @@
         <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>-0.02170778183589782</v>
+        <v>-0.05186201299004352</v>
       </c>
       <c r="EY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA10" t="n">
-        <v>-0.0100351202489004</v>
+        <v>0.1360107434846744</v>
       </c>
       <c r="FB10" t="n">
-        <v>-0.02801118641998965</v>
+        <v>-0.01408906752845598</v>
       </c>
       <c r="FC10" t="n">
         <v>0</v>
@@ -6034,10 +6034,10 @@
         <v>0</v>
       </c>
       <c r="FF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG10" t="n">
-        <v>-0.01919504282158693</v>
+        <v>0.02037705979328714</v>
       </c>
       <c r="FH10" t="n">
         <v>0</v>
@@ -6046,10 +6046,10 @@
         <v>-0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.03271603947126089</v>
+        <v>0.1025152506907377</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.137086263188218</v>
+        <v>0.1304038136263989</v>
       </c>
       <c r="FL10" t="n">
         <v>0</v>
@@ -6058,55 +6058,55 @@
         <v>-0</v>
       </c>
       <c r="FN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO10" t="n">
         <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.006874328941389774</v>
+        <v>-0.00223556610480653</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FR10" t="n">
         <v>-0</v>
       </c>
       <c r="FS10" t="n">
-        <v>-0.003883166346934424</v>
+        <v>0.2210809078858074</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.05673722225611577</v>
+        <v>0.08067260728777191</v>
       </c>
       <c r="FU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW10" t="n">
         <v>0</v>
       </c>
       <c r="FX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.0228452863997156</v>
+        <v>0.02129391826527634</v>
       </c>
       <c r="FZ10" t="n">
         <v>0</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>-0.0206624363860247</v>
+        <v>0.1929048205225777</v>
       </c>
       <c r="GC10" t="n">
         <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
@@ -7261,25 +7261,25 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.4942531038937779</v>
+        <v>0.2766264583203223</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.2003421129275067</v>
+        <v>-0.2047057192199911</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0232506114601121</v>
+        <v>-0.02704979396620259</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -7288,103 +7288,103 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3162791940053141</v>
+        <v>0.2835448566132224</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.2392127635036634</v>
+        <v>-0.2869792467700501</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.03104008881434384</v>
+        <v>-0.1106885253345132</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.106712465209628</v>
+        <v>0.04786479711326487</v>
       </c>
       <c r="U13" t="n">
         <v>-0</v>
       </c>
       <c r="V13" t="n">
-        <v>0.001450424563417655</v>
+        <v>-0.07860079678304199</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1750925923993139</v>
+        <v>-0.09260802772355385</v>
       </c>
       <c r="X13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
         <v>-0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.09368628806537953</v>
+        <v>-0.04588321727293433</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.03781547005352454</v>
+        <v>-0.1352497476527444</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.04935581369629214</v>
+        <v>-0.0658703261737117</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>-0.01573237717676269</v>
+        <v>0.1055084093045404</v>
       </c>
       <c r="AM13" t="n">
         <v>-0</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0.05809001854277469</v>
+        <v>-0.1248714300500356</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.009100228087992827</v>
+        <v>0.04503825310180141</v>
       </c>
       <c r="AP13" t="n">
         <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
         <v>-0</v>
@@ -7396,25 +7396,25 @@
         <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.4469640425451719</v>
+        <v>0.2642582365730399</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.08266005563754321</v>
+        <v>-0.07830743495504304</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.161803408173897</v>
+        <v>-0.244167801392928</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
         <v>-0</v>
@@ -7423,25 +7423,25 @@
         <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.07507832810265984</v>
+        <v>0.0005035966996062354</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>-0.2348437197868263</v>
+        <v>-0.04096009331836469</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.1642132558249735</v>
+        <v>-0.02868232370371351</v>
       </c>
       <c r="BH13" t="n">
         <v>0</v>
       </c>
       <c r="BI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
         <v>0</v>
@@ -7450,100 +7450,100 @@
         <v>-0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.1007205421649332</v>
+        <v>0.02754469222453918</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.0003122925467987326</v>
+        <v>0.05320174928147817</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.1834007035540848</v>
+        <v>0.04493566712254692</v>
       </c>
       <c r="BQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
         <v>-0</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU13" t="n">
         <v>0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.1591665273163211</v>
+        <v>0.1454782472638513</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.04286167345016913</v>
+        <v>-0.1286625429246381</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.1098461336855119</v>
+        <v>-0.06587309090989268</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
       </c>
       <c r="CB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD13" t="n">
         <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.1127147377401773</v>
+        <v>-0.09058108760943806</v>
       </c>
       <c r="CF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG13" t="n">
-        <v>-0.003866156799159154</v>
+        <v>0.1204768346232362</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.01882504733077761</v>
+        <v>0.01686335967415106</v>
       </c>
       <c r="CI13" t="n">
         <v>-0</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK13" t="n">
         <v>0</v>
       </c>
       <c r="CL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.004501660296753534</v>
+        <v>-0.0459837776374783</v>
       </c>
       <c r="CO13" t="n">
         <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>-0.1796609061390635</v>
+        <v>0.1967778577732925</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.06644724906704468</v>
+        <v>0.07535969340983042</v>
       </c>
       <c r="CR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS13" t="n">
         <v>-0</v>
@@ -7555,19 +7555,19 @@
         <v>-0</v>
       </c>
       <c r="CV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.08107589640488842</v>
+        <v>-0.08768806748839857</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.03099795808923086</v>
+        <v>0.1291847113423081</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.03048802914109129</v>
+        <v>0.03182728775788272</v>
       </c>
       <c r="DA13" t="n">
         <v>0</v>
@@ -7576,25 +7576,25 @@
         <v>0</v>
       </c>
       <c r="DC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.02975571975817543</v>
+        <v>-0.04151082021895714</v>
       </c>
       <c r="DG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.06739248010500351</v>
+        <v>0.04294615169234998</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.04221343931268737</v>
+        <v>-0.1185210000388986</v>
       </c>
       <c r="DJ13" t="n">
         <v>-0</v>
@@ -7609,28 +7609,28 @@
         <v>0</v>
       </c>
       <c r="DN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.06616717542831518</v>
+        <v>-0.07609158041008506</v>
       </c>
       <c r="DP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0.00981490446253675</v>
+        <v>-0.0507296923630178</v>
       </c>
       <c r="DR13" t="n">
-        <v>-0.04685391607527426</v>
+        <v>-0.002372506590899679</v>
       </c>
       <c r="DS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT13" t="n">
         <v>-0</v>
       </c>
       <c r="DU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV13" t="n">
         <v>0</v>
@@ -7639,43 +7639,43 @@
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0.04774019146074676</v>
+        <v>-0.007903686273637991</v>
       </c>
       <c r="DY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>-0.04336270628212117</v>
+        <v>0.08042657475152824</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.06616351193820055</v>
+        <v>-0.04037204398791028</v>
       </c>
       <c r="EB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC13" t="n">
         <v>-0</v>
       </c>
       <c r="ED13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF13" t="n">
         <v>0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.09604024533339073</v>
+        <v>-0.06152661296622648</v>
       </c>
       <c r="EH13" t="n">
         <v>-0</v>
       </c>
       <c r="EI13" t="n">
-        <v>-0.02035341771292247</v>
+        <v>0.08967693616988059</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.08050377955245973</v>
+        <v>0.05861424864247198</v>
       </c>
       <c r="EK13" t="n">
         <v>0</v>
@@ -7687,22 +7687,22 @@
         <v>0</v>
       </c>
       <c r="EN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.003865709962078615</v>
+        <v>0.009415138834501837</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.02724173371354801</v>
+        <v>0.07216141296318235</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.01557977567127668</v>
+        <v>-0.0178172235659907</v>
       </c>
       <c r="ET13" t="n">
         <v>0</v>
@@ -7720,43 +7720,43 @@
         <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.07910260443946224</v>
+        <v>-0.09671320175086731</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA13" t="n">
-        <v>-0.02035324630879624</v>
+        <v>0.1544020513213872</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.002913091624481731</v>
+        <v>0.007215015552809207</v>
       </c>
       <c r="FC13" t="n">
         <v>-0</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG13" t="n">
         <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.00839447206334879</v>
+        <v>0.1138006270797239</v>
       </c>
       <c r="FI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ13" t="n">
-        <v>-0.008311894763065901</v>
+        <v>0.09305758115648928</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.01166208326351084</v>
+        <v>0.001154803930828986</v>
       </c>
       <c r="FL13" t="n">
         <v>-0</v>
@@ -7768,55 +7768,55 @@
         <v>-0</v>
       </c>
       <c r="FO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.03689351414768441</v>
+        <v>0.04249274646129943</v>
       </c>
       <c r="FR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.03066087777583268</v>
+        <v>0.15476697359154</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.04955948773739147</v>
+        <v>-0.02237079428528752</v>
       </c>
       <c r="FU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX13" t="n">
         <v>0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.05813424456966693</v>
+        <v>-0.006960231568948204</v>
       </c>
       <c r="GA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB13" t="n">
-        <v>-0.1260786021063981</v>
+        <v>0.06564577866123338</v>
       </c>
       <c r="GC13" t="n">
         <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF13" t="n">
         <v>0</v>
@@ -7830,7 +7830,7 @@
         <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1481398042953653</v>
+        <v>0.2867389941473343</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -7839,25 +7839,25 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.05683888582503532</v>
+        <v>-0.002185340557163701</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.08862025953904987</v>
+        <v>-0.1311167807284135</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1225666288506492</v>
+        <v>0.3299839075115743</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -7866,67 +7866,67 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.04287004788463988</v>
+        <v>-0.08946640395170932</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.07944988072606217</v>
+        <v>-0.161581062626781</v>
       </c>
       <c r="P14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.01213667562667521</v>
+        <v>0.07707462294799639</v>
       </c>
       <c r="U14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.007751211507219503</v>
+        <v>-0.09561908797050984</v>
       </c>
       <c r="X14" t="n">
-        <v>0.01462862258436056</v>
+        <v>-0.01316965574990733</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0.01117908702670508</v>
+        <v>-0.03775319704528036</v>
       </c>
       <c r="AD14" t="n">
         <v>-0</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.0207404545073269</v>
+        <v>-0.1832405658468431</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.007564967116385509</v>
+        <v>0.03837398901844639</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI14" t="n">
         <v>-0</v>
@@ -7938,22 +7938,22 @@
         <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.009557523397016491</v>
+        <v>0.01933226618961996</v>
       </c>
       <c r="AM14" t="n">
         <v>-0</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.01460612805046787</v>
+        <v>-0.03936121126172785</v>
       </c>
       <c r="AP14" t="n">
-        <v>-0.01309755081503577</v>
+        <v>0.0009490826491727601</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR14" t="n">
         <v>-0</v>
@@ -7962,10 +7962,10 @@
         <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.1124712266714815</v>
+        <v>0.2549471981969477</v>
       </c>
       <c r="AV14" t="n">
         <v>-0</v>
@@ -7974,25 +7974,25 @@
         <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>-0.02006820737662953</v>
+        <v>-0.2529707483487046</v>
       </c>
       <c r="AY14" t="n">
-        <v>-0.02340704453475936</v>
+        <v>-0.09564550689711204</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA14" t="n">
         <v>-0</v>
       </c>
       <c r="BB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
         <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.04375176278624074</v>
+        <v>0.01135276326942448</v>
       </c>
       <c r="BE14" t="n">
         <v>0</v>
@@ -8001,52 +8001,52 @@
         <v>0</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.05737922290596961</v>
+        <v>0.01572051804038501</v>
       </c>
       <c r="BH14" t="n">
-        <v>-0.07125934728028509</v>
+        <v>-0.07026307683350373</v>
       </c>
       <c r="BI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK14" t="n">
         <v>0</v>
       </c>
       <c r="BL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.04298200949582174</v>
+        <v>0.02510179911206898</v>
       </c>
       <c r="BN14" t="n">
         <v>-0</v>
       </c>
       <c r="BO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.0216982448457494</v>
+        <v>0.07013688051066193</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.02265668704704907</v>
+        <v>-0.007019285950235061</v>
       </c>
       <c r="BR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS14" t="n">
         <v>-0</v>
       </c>
       <c r="BT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.04822612967337914</v>
+        <v>0.1298118751674986</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
@@ -8055,10 +8055,10 @@
         <v>0</v>
       </c>
       <c r="BY14" t="n">
-        <v>-0.01059269298858884</v>
+        <v>-0.05953145078617916</v>
       </c>
       <c r="BZ14" t="n">
-        <v>-0.005661974635233767</v>
+        <v>-0.08939735883055897</v>
       </c>
       <c r="CA14" t="n">
         <v>-0</v>
@@ -8067,40 +8067,40 @@
         <v>-0</v>
       </c>
       <c r="CC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE14" t="n">
-        <v>-0.02615301034421866</v>
+        <v>-0.08427750557373168</v>
       </c>
       <c r="CF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG14" t="n">
         <v>-0</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.003785996121969079</v>
+        <v>0.01914856115200807</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.0240425162041052</v>
+        <v>0.04899377497770723</v>
       </c>
       <c r="CJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL14" t="n">
         <v>0</v>
       </c>
       <c r="CM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN14" t="n">
-        <v>-0.007342508910834113</v>
+        <v>-0.03894967891613714</v>
       </c>
       <c r="CO14" t="n">
         <v>-0</v>
@@ -8109,64 +8109,64 @@
         <v>-0</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.001416814711860617</v>
+        <v>0.1235390436201934</v>
       </c>
       <c r="CR14" t="n">
-        <v>-0.01976221676405917</v>
+        <v>0.07325352882634634</v>
       </c>
       <c r="CS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW14" t="n">
-        <v>-0.01960761265161909</v>
+        <v>-0.08768812575293</v>
       </c>
       <c r="CX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY14" t="n">
         <v>0</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.006079873511197578</v>
+        <v>0.0130081279366955</v>
       </c>
       <c r="DA14" t="n">
-        <v>0.02284139698710073</v>
+        <v>0.06771247131784713</v>
       </c>
       <c r="DB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE14" t="n">
         <v>-0</v>
       </c>
       <c r="DF14" t="n">
-        <v>-0.01566799265493428</v>
+        <v>-0.01805445411151448</v>
       </c>
       <c r="DG14" t="n">
         <v>-0</v>
       </c>
       <c r="DH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.02333060587699535</v>
+        <v>-0.1147783193663234</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0.01004606882528751</v>
+        <v>0.05559213152114804</v>
       </c>
       <c r="DK14" t="n">
         <v>-0</v>
@@ -8175,82 +8175,82 @@
         <v>-0</v>
       </c>
       <c r="DM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN14" t="n">
         <v>-0</v>
       </c>
       <c r="DO14" t="n">
-        <v>-0.005974474677682353</v>
+        <v>-0.01219058602183311</v>
       </c>
       <c r="DP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.0185319261563807</v>
+        <v>-0.0782208440716719</v>
       </c>
       <c r="DS14" t="n">
-        <v>-0.008884444811739483</v>
+        <v>0.05210334733385216</v>
       </c>
       <c r="DT14" t="n">
         <v>-0</v>
       </c>
       <c r="DU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>-0.04059303032670063</v>
+        <v>0.01374112968687091</v>
       </c>
       <c r="DY14" t="n">
         <v>0</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.01858749638272555</v>
+        <v>-0.02373645872642204</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.01003293465360842</v>
+        <v>0.01868236548417964</v>
       </c>
       <c r="EC14" t="n">
         <v>-0</v>
       </c>
       <c r="ED14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG14" t="n">
-        <v>-0.02987912468631474</v>
+        <v>-0.04508422972241225</v>
       </c>
       <c r="EH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.005588120253610412</v>
+        <v>0.02070290086520898</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.02153772040078589</v>
+        <v>-0.002288457166588277</v>
       </c>
       <c r="EL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM14" t="n">
         <v>-0</v>
@@ -8259,82 +8259,82 @@
         <v>-0</v>
       </c>
       <c r="EO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP14" t="n">
-        <v>-0.00973995915410107</v>
+        <v>-0.007358315980661683</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER14" t="n">
         <v>-0</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.00446907583703976</v>
+        <v>-0.004725628303116764</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.005689230536522158</v>
+        <v>0.09683818923990482</v>
       </c>
       <c r="EU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV14" t="n">
         <v>0</v>
       </c>
       <c r="EW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY14" t="n">
-        <v>-0.02092397221541939</v>
+        <v>-0.09720029432275026</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA14" t="n">
         <v>-0</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.009896254455966008</v>
+        <v>0.001377048816680159</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.02814845971583319</v>
+        <v>0.04031791267591178</v>
       </c>
       <c r="FD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE14" t="n">
         <v>-0</v>
       </c>
       <c r="FF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG14" t="n">
         <v>0</v>
       </c>
       <c r="FH14" t="n">
-        <v>-0.02258957249779659</v>
+        <v>0.1752828817143068</v>
       </c>
       <c r="FI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ14" t="n">
         <v>-0</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.007059616501889136</v>
+        <v>-0.0662449704822803</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.01575215635717156</v>
+        <v>0.1182926183692563</v>
       </c>
       <c r="FM14" t="n">
         <v>0</v>
       </c>
       <c r="FN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO14" t="n">
         <v>0</v>
@@ -8343,55 +8343,55 @@
         <v>0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0.005694978102886096</v>
+        <v>0.05590090334821546</v>
       </c>
       <c r="FR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS14" t="n">
         <v>-0</v>
       </c>
       <c r="FT14" t="n">
-        <v>-0.02154825294052234</v>
+        <v>-0.08877952237421309</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.0113181127169747</v>
+        <v>-0.02160653227432588</v>
       </c>
       <c r="FV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>-0.0001761093637780886</v>
+        <v>-0.03174848011705689</v>
       </c>
       <c r="GA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB14" t="n">
         <v>-0</v>
       </c>
       <c r="GC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD14" t="n">
-        <v>-0.009656621994677785</v>
+        <v>0.06364447357774881</v>
       </c>
       <c r="GE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -8399,25 +8399,25 @@
         <v>0</v>
       </c>
       <c r="B15" t="n">
-        <v>0.5229012668337307</v>
+        <v>0.2435367928169327</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.204512668128021</v>
+        <v>-0.1898202253069566</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0743495082651178</v>
+        <v>-0.03406833390342608</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -8426,16 +8426,16 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3460115191743168</v>
+        <v>0.2666228230737009</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2134729624763103</v>
+        <v>-0.2385812952608206</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.07691526807786453</v>
+        <v>-0.0847457703883419</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -8453,76 +8453,76 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.11662226385418</v>
+        <v>0.05088194175175877</v>
       </c>
       <c r="U15" t="n">
         <v>-0</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.01790318825222273</v>
+        <v>-0.05236023289562172</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1057986902770857</v>
+        <v>-0.06861908132799732</v>
       </c>
       <c r="X15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
         <v>-0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.03550488775456589</v>
+        <v>-0.06808878883372645</v>
       </c>
       <c r="AD15" t="n">
         <v>-0</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0.01811714528708958</v>
+        <v>-0.1171632660882548</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.0135563003701158</v>
+        <v>-0.08379004433668227</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.01994209381804889</v>
+        <v>0.08929877205473971</v>
       </c>
       <c r="AM15" t="n">
         <v>-0</v>
       </c>
       <c r="AN15" t="n">
-        <v>-0.06592031360716154</v>
+        <v>-0.09887288705499286</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.04980570983601924</v>
+        <v>0.02467078125019109</v>
       </c>
       <c r="AP15" t="n">
         <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
         <v>-0</v>
@@ -8531,28 +8531,28 @@
         <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.4615923192484491</v>
+        <v>0.2353007247031296</v>
       </c>
       <c r="AV15" t="n">
         <v>-0</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.02730855973161331</v>
+        <v>-0.07363913122604646</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.09639047074336678</v>
+        <v>-0.1900519961043317</v>
       </c>
       <c r="AY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
         <v>-0</v>
@@ -8561,25 +8561,25 @@
         <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.04816984941337859</v>
+        <v>-0.006732922733127214</v>
       </c>
       <c r="BE15" t="n">
         <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>-0.2044110608251782</v>
+        <v>-0.05930133784042118</v>
       </c>
       <c r="BG15" t="n">
-        <v>-0.1327968400909841</v>
+        <v>-0.002205791109399593</v>
       </c>
       <c r="BH15" t="n">
         <v>0</v>
       </c>
       <c r="BI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK15" t="n">
         <v>0</v>
@@ -8588,19 +8588,19 @@
         <v>-0</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.1429126353796081</v>
+        <v>0.01209157858051325</v>
       </c>
       <c r="BN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.04412394914329774</v>
+        <v>0.06169860331251825</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.1801301813702823</v>
+        <v>0.05487623917104614</v>
       </c>
       <c r="BQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR15" t="n">
         <v>0</v>
@@ -8609,55 +8609,55 @@
         <v>-0</v>
       </c>
       <c r="BT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU15" t="n">
         <v>0</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.1845918586948874</v>
+        <v>0.1393062148631787</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.01054247155495059</v>
+        <v>-0.1051198524776421</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.05875919826532092</v>
+        <v>-0.02952719319057751</v>
       </c>
       <c r="BZ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA15" t="n">
         <v>-0</v>
       </c>
       <c r="CB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD15" t="n">
         <v>-0</v>
       </c>
       <c r="CE15" t="n">
-        <v>-0.09902593643885969</v>
+        <v>-0.06727280099522349</v>
       </c>
       <c r="CF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.007628023627445876</v>
+        <v>0.1019777573952056</v>
       </c>
       <c r="CH15" t="n">
-        <v>-0.01227854569447757</v>
+        <v>0.01633765651962083</v>
       </c>
       <c r="CI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK15" t="n">
         <v>0</v>
@@ -8669,25 +8669,25 @@
         <v>0</v>
       </c>
       <c r="CN15" t="n">
-        <v>-0.008852157867306649</v>
+        <v>-0.05507071375974017</v>
       </c>
       <c r="CO15" t="n">
         <v>-0</v>
       </c>
       <c r="CP15" t="n">
-        <v>-0.09508999559757909</v>
+        <v>0.1459022213271928</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0.0865747168585619</v>
+        <v>0.0418970250781895</v>
       </c>
       <c r="CR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS15" t="n">
         <v>-0</v>
       </c>
       <c r="CT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU15" t="n">
         <v>-0</v>
@@ -8696,16 +8696,16 @@
         <v>0</v>
       </c>
       <c r="CW15" t="n">
-        <v>-0.06571728978007127</v>
+        <v>-0.06509662102898092</v>
       </c>
       <c r="CX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.04501573471146228</v>
+        <v>0.1062297591468065</v>
       </c>
       <c r="CZ15" t="n">
-        <v>-0.01962530193135796</v>
+        <v>0.02818707759487207</v>
       </c>
       <c r="DA15" t="n">
         <v>0</v>
@@ -8717,22 +8717,22 @@
         <v>-0</v>
       </c>
       <c r="DD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>-0.05450510332364859</v>
+        <v>-0.06773946547983792</v>
       </c>
       <c r="DG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.05907036854236362</v>
+        <v>0.02581282978745509</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.03179692181796308</v>
+        <v>-0.02949535966500404</v>
       </c>
       <c r="DJ15" t="n">
         <v>-0</v>
@@ -8747,28 +8747,28 @@
         <v>0</v>
       </c>
       <c r="DN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>-0.07492280692648229</v>
+        <v>-0.05815322034674444</v>
       </c>
       <c r="DP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ15" t="n">
-        <v>-0.001993903179798514</v>
+        <v>-0.02845935114823843</v>
       </c>
       <c r="DR15" t="n">
-        <v>-0.04116180343214585</v>
+        <v>0.004511645080942874</v>
       </c>
       <c r="DS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT15" t="n">
         <v>-0</v>
       </c>
       <c r="DU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV15" t="n">
         <v>0</v>
@@ -8777,16 +8777,16 @@
         <v>-0</v>
       </c>
       <c r="DX15" t="n">
-        <v>-0.09891410546413103</v>
+        <v>0.01618037878212415</v>
       </c>
       <c r="DY15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>-0.008712622491505848</v>
+        <v>0.0760369192483628</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.04014214508110332</v>
+        <v>-0.0632675240370478</v>
       </c>
       <c r="EB15" t="n">
         <v>-0</v>
@@ -8798,55 +8798,55 @@
         <v>0</v>
       </c>
       <c r="EE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG15" t="n">
-        <v>-0.08542420414710505</v>
+        <v>-0.03639384211287433</v>
       </c>
       <c r="EH15" t="n">
         <v>-0</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.01153838287161876</v>
+        <v>0.06616218420622821</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.07023521832915937</v>
+        <v>0.05768244002147054</v>
       </c>
       <c r="EK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.001519718968702025</v>
+        <v>-0.007007524500797763</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER15" t="n">
-        <v>-0.0007508970353946981</v>
+        <v>0.06940857547623062</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.02941266936078334</v>
+        <v>-0.03577011288329646</v>
       </c>
       <c r="ET15" t="n">
         <v>0</v>
       </c>
       <c r="EU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV15" t="n">
         <v>0</v>
@@ -8858,22 +8858,22 @@
         <v>-0</v>
       </c>
       <c r="EY15" t="n">
-        <v>-0.06519280232287525</v>
+        <v>-0.07072698841273371</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA15" t="n">
-        <v>0.005587272474343812</v>
+        <v>0.1271655521741017</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.01295276634577782</v>
+        <v>0.005299678821235181</v>
       </c>
       <c r="FC15" t="n">
         <v>-0</v>
       </c>
       <c r="FD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE15" t="n">
         <v>0</v>
@@ -8885,16 +8885,16 @@
         <v>0</v>
       </c>
       <c r="FH15" t="n">
-        <v>-0.06652828071306019</v>
+        <v>0.1036861299187363</v>
       </c>
       <c r="FI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0.00140190442199003</v>
+        <v>0.07593070839758753</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.05154739593120509</v>
+        <v>-0.05199956040787138</v>
       </c>
       <c r="FL15" t="n">
         <v>-0</v>
@@ -8906,58 +8906,58 @@
         <v>-0</v>
       </c>
       <c r="FO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>-0.05226651146357128</v>
+        <v>0.04169365874888128</v>
       </c>
       <c r="FR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.01495081939353681</v>
+        <v>0.1358182041476814</v>
       </c>
       <c r="FT15" t="n">
-        <v>-0.0701114479294523</v>
+        <v>-0.04890175363750773</v>
       </c>
       <c r="FU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX15" t="n">
         <v>0</v>
       </c>
       <c r="FY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.06901262679419413</v>
+        <v>-0.01069164982756855</v>
       </c>
       <c r="GA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB15" t="n">
-        <v>-0.1243668939888392</v>
+        <v>0.03762842895895696</v>
       </c>
       <c r="GC15" t="n">
         <v>-0</v>
       </c>
       <c r="GD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG15" t="n">
         <v>-0</v>
@@ -8968,7 +8968,7 @@
         <v>-0</v>
       </c>
       <c r="B16" t="n">
-        <v>-1.038419593616752</v>
+        <v>-0.3598538033021381</v>
       </c>
       <c r="C16" t="n">
         <v>-0</v>
@@ -8977,13 +8977,13 @@
         <v>-0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1763688916383872</v>
+        <v>0.1447877350110121</v>
       </c>
       <c r="F16" t="n">
-        <v>1.312638176469514</v>
+        <v>0.5690662786681395</v>
       </c>
       <c r="G16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -8992,10 +8992,10 @@
         <v>-0</v>
       </c>
       <c r="J16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.9318034508347223</v>
+        <v>-0.5988089030890421</v>
       </c>
       <c r="L16" t="n">
         <v>-0</v>
@@ -9004,10 +9004,10 @@
         <v>-0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.08094752131217563</v>
+        <v>0.2169975748962903</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9884653486601698</v>
+        <v>0.6669476360858031</v>
       </c>
       <c r="P16" t="n">
         <v>-0</v>
@@ -9016,40 +9016,40 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.112610142892803</v>
+        <v>-0.1043603335293944</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V16" t="n">
         <v>-0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2524508687553755</v>
+        <v>0.1358308551060846</v>
       </c>
       <c r="X16" t="n">
-        <v>0.1358946927891981</v>
+        <v>0.09488150394744249</v>
       </c>
       <c r="Y16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.009651045391303343</v>
+        <v>0.002314155986012001</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -9058,10 +9058,10 @@
         <v>-0</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.193608182827803</v>
+        <v>0.1948716271029817</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.1482331740649096</v>
+        <v>-0.01656517047179552</v>
       </c>
       <c r="AH16" t="n">
         <v>-0</v>
@@ -9070,28 +9070,28 @@
         <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK16" t="n">
         <v>-0</v>
       </c>
       <c r="AL16" t="n">
-        <v>-0.1308196260071463</v>
+        <v>-0.0648346710742085</v>
       </c>
       <c r="AM16" t="n">
         <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.03813244437693974</v>
+        <v>0.02262649640714098</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.2863337803670134</v>
+        <v>0.09203938831350567</v>
       </c>
       <c r="AQ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -9100,37 +9100,37 @@
         <v>-0</v>
       </c>
       <c r="AT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>-0.6785572356005819</v>
+        <v>-0.7210090980146151</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW16" t="n">
         <v>-0</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.2380029165169435</v>
+        <v>0.0704952861285584</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.826859738762723</v>
+        <v>0.4182648914162843</v>
       </c>
       <c r="AZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD16" t="n">
-        <v>-0.3064723916609943</v>
+        <v>0.1894188920039362</v>
       </c>
       <c r="BE16" t="n">
         <v>-0</v>
@@ -9139,10 +9139,10 @@
         <v>-0</v>
       </c>
       <c r="BG16" t="n">
-        <v>0.1465660194973738</v>
+        <v>0.1305842173038882</v>
       </c>
       <c r="BH16" t="n">
-        <v>0.3658529719287963</v>
+        <v>0.005938686282085949</v>
       </c>
       <c r="BI16" t="n">
         <v>-0</v>
@@ -9154,49 +9154,49 @@
         <v>-0</v>
       </c>
       <c r="BL16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM16" t="n">
-        <v>-0.3139920853836689</v>
+        <v>-0.1967224964909011</v>
       </c>
       <c r="BN16" t="n">
         <v>0</v>
       </c>
       <c r="BO16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP16" t="n">
-        <v>-0.1299092721315395</v>
+        <v>-0.159201263233138</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0.009994040934758504</v>
+        <v>-0.1119834861835583</v>
       </c>
       <c r="BR16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT16" t="n">
         <v>-0</v>
       </c>
       <c r="BU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV16" t="n">
-        <v>-0.4945109049324968</v>
+        <v>-0.3726471003849079</v>
       </c>
       <c r="BW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX16" t="n">
         <v>-0</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.08381829151887522</v>
+        <v>0.01329113330380518</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.4136849997653558</v>
+        <v>0.2618392113279792</v>
       </c>
       <c r="CA16" t="n">
         <v>0</v>
@@ -9205,28 +9205,28 @@
         <v>0</v>
       </c>
       <c r="CC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE16" t="n">
-        <v>0.1835444645177321</v>
+        <v>0.1098900252221394</v>
       </c>
       <c r="CF16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG16" t="n">
         <v>0</v>
       </c>
       <c r="CH16" t="n">
-        <v>-0.01451763811154963</v>
+        <v>-0.07664631096238433</v>
       </c>
       <c r="CI16" t="n">
-        <v>-0.2019502716257978</v>
+        <v>-0.1557206000337656</v>
       </c>
       <c r="CJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK16" t="n">
         <v>-0</v>
@@ -9238,7 +9238,7 @@
         <v>-0</v>
       </c>
       <c r="CN16" t="n">
-        <v>0.06998749323660716</v>
+        <v>0.2129520690357828</v>
       </c>
       <c r="CO16" t="n">
         <v>0</v>
@@ -9247,16 +9247,16 @@
         <v>0</v>
       </c>
       <c r="CQ16" t="n">
-        <v>-0.148575783448276</v>
+        <v>-0.03824096363973033</v>
       </c>
       <c r="CR16" t="n">
-        <v>0.06699828392304562</v>
+        <v>-0.02662092544090739</v>
       </c>
       <c r="CS16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU16" t="n">
         <v>0</v>
@@ -9265,22 +9265,22 @@
         <v>0</v>
       </c>
       <c r="CW16" t="n">
-        <v>0.1557313168819517</v>
+        <v>0.1020624283063025</v>
       </c>
       <c r="CX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY16" t="n">
         <v>-0</v>
       </c>
       <c r="CZ16" t="n">
-        <v>-0.0242644800655756</v>
+        <v>-0.07350308369778408</v>
       </c>
       <c r="DA16" t="n">
-        <v>-0.2295893520580498</v>
+        <v>-0.177448072569979</v>
       </c>
       <c r="DB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC16" t="n">
         <v>0</v>
@@ -9289,76 +9289,76 @@
         <v>-0</v>
       </c>
       <c r="DE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>0.2611764070439779</v>
+        <v>0.1097201406878574</v>
       </c>
       <c r="DG16" t="n">
         <v>0</v>
       </c>
       <c r="DH16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI16" t="n">
-        <v>-0.3413551281289368</v>
+        <v>0.1007181515483703</v>
       </c>
       <c r="DJ16" t="n">
-        <v>0.02235696226555267</v>
+        <v>-0.01035027045190103</v>
       </c>
       <c r="DK16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL16" t="n">
         <v>-0</v>
       </c>
       <c r="DM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO16" t="n">
-        <v>0.05854964316706099</v>
+        <v>-0.0200104534476439</v>
       </c>
       <c r="DP16" t="n">
         <v>-0</v>
       </c>
       <c r="DQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR16" t="n">
-        <v>-0.01888416976927257</v>
+        <v>0.04844659028340872</v>
       </c>
       <c r="DS16" t="n">
-        <v>-0.1044679929487424</v>
+        <v>-0.1476660306078367</v>
       </c>
       <c r="DT16" t="n">
         <v>0</v>
       </c>
       <c r="DU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX16" t="n">
-        <v>0.1759509910431648</v>
+        <v>0.1240014157418528</v>
       </c>
       <c r="DY16" t="n">
         <v>0</v>
       </c>
       <c r="DZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA16" t="n">
-        <v>-0.1233759208467229</v>
+        <v>0.01613028447302936</v>
       </c>
       <c r="EB16" t="n">
-        <v>-0.07123893237190511</v>
+        <v>-0.0218448018657464</v>
       </c>
       <c r="EC16" t="n">
         <v>0</v>
@@ -9367,28 +9367,28 @@
         <v>-0</v>
       </c>
       <c r="EE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG16" t="n">
-        <v>0.1305958031229554</v>
+        <v>0.0384955283748793</v>
       </c>
       <c r="EH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ16" t="n">
-        <v>-0.07905310564212403</v>
+        <v>-0.03328808766454955</v>
       </c>
       <c r="EK16" t="n">
-        <v>-0.2144349264329201</v>
+        <v>-0.05869544107058682</v>
       </c>
       <c r="EL16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM16" t="n">
         <v>0</v>
@@ -9400,34 +9400,34 @@
         <v>-0</v>
       </c>
       <c r="EP16" t="n">
-        <v>0.1160571834167134</v>
+        <v>0.05287081292407506</v>
       </c>
       <c r="EQ16" t="n">
         <v>0</v>
       </c>
       <c r="ER16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES16" t="n">
-        <v>-0.01967584932149626</v>
+        <v>-0.06177107204423184</v>
       </c>
       <c r="ET16" t="n">
-        <v>-0.03626474975207668</v>
+        <v>0.1446888234612238</v>
       </c>
       <c r="EU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV16" t="n">
         <v>-0</v>
       </c>
       <c r="EW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX16" t="n">
         <v>-0</v>
       </c>
       <c r="EY16" t="n">
-        <v>0.1554498101315428</v>
+        <v>0.1285380108704607</v>
       </c>
       <c r="EZ16" t="n">
         <v>0</v>
@@ -9436,13 +9436,13 @@
         <v>0</v>
       </c>
       <c r="FB16" t="n">
-        <v>-0.05236032358751428</v>
+        <v>-0.03459604782082719</v>
       </c>
       <c r="FC16" t="n">
-        <v>-0.211755955078467</v>
+        <v>-0.1589022651176666</v>
       </c>
       <c r="FD16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE16" t="n">
         <v>-0</v>
@@ -9454,7 +9454,7 @@
         <v>-0</v>
       </c>
       <c r="FH16" t="n">
-        <v>0.03610253091764849</v>
+        <v>-0.08378084123043972</v>
       </c>
       <c r="FI16" t="n">
         <v>-0</v>
@@ -9463,10 +9463,10 @@
         <v>0</v>
       </c>
       <c r="FK16" t="n">
-        <v>-0.005844069189057595</v>
+        <v>0.07677368577523293</v>
       </c>
       <c r="FL16" t="n">
-        <v>-0.1864870234805785</v>
+        <v>-0.09235530607730361</v>
       </c>
       <c r="FM16" t="n">
         <v>-0</v>
@@ -9478,10 +9478,10 @@
         <v>-0</v>
       </c>
       <c r="FP16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>-0.00506442113838855</v>
+        <v>0.02695572400511593</v>
       </c>
       <c r="FR16" t="n">
         <v>0</v>
@@ -9490,69 +9490,69 @@
         <v>0</v>
       </c>
       <c r="FT16" t="n">
-        <v>0.119416934262463</v>
+        <v>0.148610238749513</v>
       </c>
       <c r="FU16" t="n">
-        <v>-0.1606672145241512</v>
+        <v>0.1618157917437069</v>
       </c>
       <c r="FV16" t="n">
         <v>0</v>
       </c>
       <c r="FW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX16" t="n">
         <v>-0</v>
       </c>
       <c r="FY16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>-0.01706139169143513</v>
+        <v>0.0390296569036009</v>
       </c>
       <c r="GA16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB16" t="n">
         <v>0</v>
       </c>
       <c r="GC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD16" t="n">
-        <v>0.1514059043677332</v>
+        <v>-0.06925896257382838</v>
       </c>
       <c r="GE16" t="n">
         <v>0</v>
       </c>
       <c r="GF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>-0.5666716748102586</v>
+        <v>-0.192833559604158</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1223775892319514</v>
+        <v>0.1138543484713079</v>
       </c>
       <c r="F17" t="n">
-        <v>1.016816289300767</v>
+        <v>0.2359478493289528</v>
       </c>
       <c r="G17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -9561,10 +9561,10 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3823038671208433</v>
+        <v>-0.1682130023708686</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L17" t="n">
         <v>-0</v>
@@ -9573,13 +9573,13 @@
         <v>-0</v>
       </c>
       <c r="N17" t="n">
-        <v>0.09763251296082553</v>
+        <v>0.2109506291289342</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8321947914262182</v>
+        <v>0.3819644866224413</v>
       </c>
       <c r="P17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -9588,142 +9588,142 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.09394374677382165</v>
+        <v>0.01823018622208819</v>
       </c>
       <c r="T17" t="n">
         <v>-0</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V17" t="n">
         <v>-0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1765543815818733</v>
+        <v>0.0009925716196015608</v>
       </c>
       <c r="X17" t="n">
-        <v>0.1545092839588635</v>
+        <v>0.04892218927673812</v>
       </c>
       <c r="Y17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0.08882254065430553</v>
+        <v>-0.01193499842582826</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
         <v>-0</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.02083353985795998</v>
+        <v>0.01241261663637922</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.0557654426323675</v>
+        <v>-0.03955768807944172</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>-0.1095325045511467</v>
+        <v>-0.03732961927673159</v>
       </c>
       <c r="AL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
         <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO17" t="n">
-        <v>-0.1171853625675836</v>
+        <v>-0.07423220934199175</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.09159810458206748</v>
+        <v>0.02398620959342083</v>
       </c>
       <c r="AQ17" t="n">
         <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT17" t="n">
-        <v>-0.4502640606911026</v>
+        <v>-0.1812804465030418</v>
       </c>
       <c r="AU17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW17" t="n">
         <v>-0</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.1990616592528826</v>
+        <v>-0.07082238795411505</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.534112262633831</v>
+        <v>0.3104703572965167</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
         <v>-0</v>
       </c>
       <c r="BC17" t="n">
-        <v>-0.1043252287049263</v>
+        <v>0.009675642597821658</v>
       </c>
       <c r="BD17" t="n">
         <v>-0</v>
       </c>
       <c r="BE17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
         <v>-0</v>
       </c>
       <c r="BG17" t="n">
-        <v>0.01443305978728432</v>
+        <v>0.1047948484690513</v>
       </c>
       <c r="BH17" t="n">
-        <v>0.2464921392185512</v>
+        <v>-0.06808454357193072</v>
       </c>
       <c r="BI17" t="n">
         <v>-0</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK17" t="n">
         <v>0</v>
       </c>
       <c r="BL17" t="n">
-        <v>-0.01285192184631394</v>
+        <v>0.0482951691557005</v>
       </c>
       <c r="BM17" t="n">
         <v>0</v>
@@ -9732,52 +9732,52 @@
         <v>0</v>
       </c>
       <c r="BO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.05240443142789012</v>
+        <v>0.03082481875461637</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.03212949633274198</v>
+        <v>-0.01631411172852623</v>
       </c>
       <c r="BR17" t="n">
         <v>0</v>
       </c>
       <c r="BS17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT17" t="n">
         <v>-0</v>
       </c>
       <c r="BU17" t="n">
-        <v>-0.1816740441699352</v>
+        <v>-0.06625896728324723</v>
       </c>
       <c r="BV17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.1341241280246304</v>
+        <v>0.09349243178047964</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.3336789992758572</v>
+        <v>0.1569145324826639</v>
       </c>
       <c r="CA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD17" t="n">
-        <v>0.1214985160028928</v>
+        <v>0.05704349107464705</v>
       </c>
       <c r="CE17" t="n">
         <v>-0</v>
@@ -9786,67 +9786,67 @@
         <v>0</v>
       </c>
       <c r="CG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH17" t="n">
-        <v>-0.05845836756908756</v>
+        <v>-0.03616633443699916</v>
       </c>
       <c r="CI17" t="n">
-        <v>-0.1793727108592815</v>
+        <v>-0.06606936635583745</v>
       </c>
       <c r="CJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK17" t="n">
         <v>-0</v>
       </c>
       <c r="CL17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM17" t="n">
-        <v>-0.01150143885000579</v>
+        <v>0.008904031054971796</v>
       </c>
       <c r="CN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CO17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP17" t="n">
         <v>0</v>
       </c>
       <c r="CQ17" t="n">
-        <v>-0.2062317737383704</v>
+        <v>-0.1051100398285744</v>
       </c>
       <c r="CR17" t="n">
-        <v>-0.05144903460547854</v>
+        <v>-0.07103315977637333</v>
       </c>
       <c r="CS17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT17" t="n">
         <v>0</v>
       </c>
       <c r="CU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV17" t="n">
-        <v>0.1147631460107972</v>
+        <v>0.06932472999392338</v>
       </c>
       <c r="CW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX17" t="n">
         <v>-0</v>
       </c>
       <c r="CY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ17" t="n">
-        <v>-0.07263684609181367</v>
+        <v>-0.06467137025800926</v>
       </c>
       <c r="DA17" t="n">
-        <v>-0.1779704511545404</v>
+        <v>-0.07641318373362849</v>
       </c>
       <c r="DB17" t="n">
         <v>0</v>
@@ -9855,37 +9855,37 @@
         <v>0</v>
       </c>
       <c r="DD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.0002549561785810551</v>
+        <v>0.002227900444944309</v>
       </c>
       <c r="DF17" t="n">
         <v>-0</v>
       </c>
       <c r="DG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI17" t="n">
-        <v>-0.01766650822032275</v>
+        <v>-0.02178993155850094</v>
       </c>
       <c r="DJ17" t="n">
-        <v>-0.007344484496597934</v>
+        <v>-0.01196314691562576</v>
       </c>
       <c r="DK17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL17" t="n">
         <v>-0</v>
       </c>
       <c r="DM17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.04530818492770356</v>
+        <v>0.009264219635454591</v>
       </c>
       <c r="DO17" t="n">
         <v>0</v>
@@ -9897,10 +9897,10 @@
         <v>-0</v>
       </c>
       <c r="DR17" t="n">
-        <v>-0.06785526390362635</v>
+        <v>-0.01860874713082384</v>
       </c>
       <c r="DS17" t="n">
-        <v>-0.1016461156496816</v>
+        <v>-0.09372707393067405</v>
       </c>
       <c r="DT17" t="n">
         <v>0</v>
@@ -9912,7 +9912,7 @@
         <v>0</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.04701208018699214</v>
+        <v>0.02470077888071191</v>
       </c>
       <c r="DX17" t="n">
         <v>-0</v>
@@ -9924,13 +9924,13 @@
         <v>-0</v>
       </c>
       <c r="EA17" t="n">
-        <v>-0.02772524475434599</v>
+        <v>-0.09603891353249613</v>
       </c>
       <c r="EB17" t="n">
-        <v>-0.1150618429997223</v>
+        <v>-0.05962940071530191</v>
       </c>
       <c r="EC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED17" t="n">
         <v>0</v>
@@ -9939,34 +9939,34 @@
         <v>-0</v>
       </c>
       <c r="EF17" t="n">
-        <v>0.0864170000224493</v>
+        <v>0.00796995975112769</v>
       </c>
       <c r="EG17" t="n">
         <v>-0</v>
       </c>
       <c r="EH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI17" t="n">
         <v>0</v>
       </c>
       <c r="EJ17" t="n">
-        <v>-0.06880776082586741</v>
+        <v>-0.03633758264519012</v>
       </c>
       <c r="EK17" t="n">
-        <v>-0.1684599307002726</v>
+        <v>-0.03055989969500748</v>
       </c>
       <c r="EL17" t="n">
         <v>0</v>
       </c>
       <c r="EM17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO17" t="n">
-        <v>-0.04674548956410186</v>
+        <v>-0.02794000425745765</v>
       </c>
       <c r="EP17" t="n">
         <v>-0</v>
@@ -9975,13 +9975,13 @@
         <v>0</v>
       </c>
       <c r="ER17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES17" t="n">
-        <v>0.1107930802205071</v>
+        <v>0.03466553626909738</v>
       </c>
       <c r="ET17" t="n">
-        <v>-0.02252245164808438</v>
+        <v>-0.03182878884494243</v>
       </c>
       <c r="EU17" t="n">
         <v>-0</v>
@@ -9990,64 +9990,64 @@
         <v>-0</v>
       </c>
       <c r="EW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX17" t="n">
-        <v>0.09814276998428162</v>
+        <v>0.06600079014888859</v>
       </c>
       <c r="EY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EZ17" t="n">
         <v>0</v>
       </c>
       <c r="FA17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB17" t="n">
-        <v>-0.08508760991689523</v>
+        <v>-0.04962452038059504</v>
       </c>
       <c r="FC17" t="n">
-        <v>-0.1669167293594808</v>
+        <v>-0.07451902560098106</v>
       </c>
       <c r="FD17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF17" t="n">
         <v>0</v>
       </c>
       <c r="FG17" t="n">
-        <v>0.05702512670781076</v>
+        <v>0.08832649745176419</v>
       </c>
       <c r="FH17" t="n">
         <v>0</v>
       </c>
       <c r="FI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ17" t="n">
         <v>0</v>
       </c>
       <c r="FK17" t="n">
-        <v>-0.04947600929827232</v>
+        <v>0.02952676680343074</v>
       </c>
       <c r="FL17" t="n">
-        <v>0.02120357344873773</v>
+        <v>-0.01125710515463258</v>
       </c>
       <c r="FM17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP17" t="n">
-        <v>0.09451059029816372</v>
+        <v>0.1167033485601641</v>
       </c>
       <c r="FQ17" t="n">
         <v>0</v>
@@ -10056,31 +10056,31 @@
         <v>0</v>
       </c>
       <c r="FS17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT17" t="n">
-        <v>-0.08697505209705916</v>
+        <v>-0.005001488335812583</v>
       </c>
       <c r="FU17" t="n">
-        <v>-0.1118622490839958</v>
+        <v>-0.1510295554275393</v>
       </c>
       <c r="FV17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX17" t="n">
         <v>-0</v>
       </c>
       <c r="FY17" t="n">
-        <v>-0.03197422620309318</v>
+        <v>-0.01328170686569166</v>
       </c>
       <c r="FZ17" t="n">
         <v>0</v>
       </c>
       <c r="GA17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB17" t="n">
         <v>0</v>
@@ -10089,16 +10089,16 @@
         <v>-0</v>
       </c>
       <c r="GD17" t="n">
-        <v>0.04157627307143422</v>
+        <v>0.0378346136822459</v>
       </c>
       <c r="GE17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
   </sheetData>
